--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_2_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_2_bus.xlsx
@@ -824,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.076309581697509</v>
+        <v>1.076309581697511</v>
       </c>
       <c r="O2">
-        <v>0.3968725684451613</v>
+        <v>0.3968725684451628</v>
       </c>
       <c r="P2">
-        <v>0.857503166648942</v>
+        <v>0.8575031666489451</v>
       </c>
       <c r="Q2">
-        <v>8.78910895020956</v>
+        <v>8.789108950209547</v>
       </c>
       <c r="R2">
-        <v>-124.0274590207981</v>
+        <v>-124.0274590207978</v>
       </c>
       <c r="S2">
-        <v>168.9429116866489</v>
+        <v>168.9429116866488</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -883,22 +883,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.044105714997498</v>
+        <v>1.0441057149975</v>
       </c>
       <c r="O3">
-        <v>0.2604212734074333</v>
+        <v>0.2604212734074349</v>
       </c>
       <c r="P3">
-        <v>0.8710642653707239</v>
+        <v>0.8710642653707271</v>
       </c>
       <c r="Q3">
-        <v>5.325452027459457</v>
+        <v>5.325452027459431</v>
       </c>
       <c r="R3">
-        <v>-131.9071155621092</v>
+        <v>-131.9071155621087</v>
       </c>
       <c r="S3">
-        <v>173.6125839687829</v>
+        <v>173.6125839687827</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -909,55 +909,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.823703257666274</v>
+        <v>1.823703257666271</v>
       </c>
       <c r="D4">
-        <v>1.823703257666274</v>
+        <v>1.823703257666271</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>21.05831133471242</v>
+        <v>21.05831133471238</v>
       </c>
       <c r="G4">
-        <v>21.05831133471242</v>
+        <v>21.05831133471238</v>
       </c>
       <c r="H4">
-        <v>5.424025632034072</v>
+        <v>4.144030571481084</v>
       </c>
       <c r="I4">
-        <v>6.488939310918614</v>
+        <v>5.855913331295394</v>
       </c>
       <c r="J4">
-        <v>2.237816431607152</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L4">
-        <v>2.237816431580072</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M4">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>0.9526279648094348</v>
+        <v>0.9526279648094378</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648098408</v>
+        <v>0.9526279648098431</v>
       </c>
       <c r="Q4">
-        <v>-2.317161082148245E-13</v>
+        <v>-2.558530584725643E-13</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.999999999992</v>
+        <v>179.9999999999919</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1001,22 +1001,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.044105714978374</v>
+        <v>1.044105714978376</v>
       </c>
       <c r="O5">
-        <v>0.2604212734211523</v>
+        <v>0.2604212734211539</v>
       </c>
       <c r="P5">
-        <v>0.8710642653956977</v>
+        <v>0.8710642653957009</v>
       </c>
       <c r="Q5">
-        <v>5.325452029148392</v>
+        <v>5.325452029148371</v>
       </c>
       <c r="R5">
-        <v>-131.9071155464532</v>
+        <v>-131.9071155464527</v>
       </c>
       <c r="S5">
-        <v>173.612583967056</v>
+        <v>173.6125839670558</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.044105714978374</v>
+        <v>1.044105714978376</v>
       </c>
       <c r="O6">
-        <v>0.2604212734211522</v>
+        <v>0.2604212734211537</v>
       </c>
       <c r="P6">
-        <v>0.8710642653956977</v>
+        <v>0.8710642653957009</v>
       </c>
       <c r="Q6">
-        <v>5.325452029148392</v>
+        <v>5.32545202914836</v>
       </c>
       <c r="R6">
-        <v>-131.9071155464532</v>
+        <v>-131.9071155464527</v>
       </c>
       <c r="S6">
-        <v>173.612583967056</v>
+        <v>173.6125839670558</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1119,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9526279646173125</v>
+        <v>0.9526279646173154</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.952627965001963</v>
+        <v>0.9526279650019653</v>
       </c>
       <c r="Q7">
-        <v>1.161106357313543E-09</v>
+        <v>1.161086075580896E-09</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9999999988307</v>
+        <v>179.9999999988306</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1178,22 +1178,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.044105714816402</v>
+        <v>1.044105714816404</v>
       </c>
       <c r="O8">
-        <v>0.2604212731841037</v>
+        <v>0.2604212731841052</v>
       </c>
       <c r="P8">
-        <v>0.8710642655544109</v>
+        <v>0.8710642655544142</v>
       </c>
       <c r="Q8">
-        <v>5.32545202917925</v>
+        <v>5.325452029179222</v>
       </c>
       <c r="R8">
-        <v>-131.9071154978766</v>
+        <v>-131.9071154978761</v>
       </c>
       <c r="S8">
-        <v>173.6125839691826</v>
+        <v>173.6125839691825</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1237,22 +1237,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.044105714816402</v>
+        <v>1.044105714816404</v>
       </c>
       <c r="O9">
-        <v>0.2604212731841036</v>
+        <v>0.2604212731841051</v>
       </c>
       <c r="P9">
-        <v>0.8710642655544109</v>
+        <v>0.8710642655544142</v>
       </c>
       <c r="Q9">
-        <v>5.32545202917925</v>
+        <v>5.32545202917921</v>
       </c>
       <c r="R9">
-        <v>-131.9071154978766</v>
+        <v>-131.9071154978761</v>
       </c>
       <c r="S9">
-        <v>173.6125839691826</v>
+        <v>173.6125839691825</v>
       </c>
     </row>
   </sheetData>
@@ -1365,22 +1365,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.105984389062563</v>
+        <v>1.105984389062562</v>
       </c>
       <c r="O2">
-        <v>0.666663779019942</v>
+        <v>0.6666637790199431</v>
       </c>
       <c r="P2">
-        <v>0.9022299634541985</v>
+        <v>0.902229963454199</v>
       </c>
       <c r="Q2">
-        <v>16.57809355178734</v>
+        <v>16.57809355178736</v>
       </c>
       <c r="R2">
-        <v>-108.7929438266823</v>
+        <v>-108.7929438266822</v>
       </c>
       <c r="S2">
-        <v>159.5275221691293</v>
+        <v>159.5275221691292</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1427,19 +1427,19 @@
         <v>1.085364253791841</v>
       </c>
       <c r="O3">
-        <v>0.5754536980987548</v>
+        <v>0.5754536980987563</v>
       </c>
       <c r="P3">
-        <v>0.8958560121999106</v>
+        <v>0.8958560121999111</v>
       </c>
       <c r="Q3">
-        <v>14.42238148354708</v>
+        <v>14.42238148354711</v>
       </c>
       <c r="R3">
-        <v>-110.0262111070278</v>
+        <v>-110.0262111070277</v>
       </c>
       <c r="S3">
-        <v>162.4369087610724</v>
+        <v>162.4369087610723</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1450,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.172096236067255</v>
+        <v>1.172096236067254</v>
       </c>
       <c r="D4">
-        <v>1.172096236067255</v>
+        <v>1.172096236067254</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1465,40 +1465,40 @@
         <v>13.53420154819153</v>
       </c>
       <c r="H4">
-        <v>5.424025632034038</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I4">
-        <v>6.488939310918608</v>
+        <v>5.855913331295392</v>
       </c>
       <c r="J4">
-        <v>2.237816431607135</v>
+        <v>2.237816431607154</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564864</v>
       </c>
       <c r="L4">
-        <v>2.237816431580052</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M4">
-        <v>5.601194464517764</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
         <v>1.024925070816898</v>
       </c>
       <c r="O4">
-        <v>0.4143985983631068</v>
+        <v>0.4143985983631084</v>
       </c>
       <c r="P4">
-        <v>0.9221668921891053</v>
+        <v>0.9221668921891056</v>
       </c>
       <c r="Q4">
-        <v>11.27752546015155</v>
+        <v>11.27752546015158</v>
       </c>
       <c r="R4">
-        <v>-104.679650256468</v>
+        <v>-104.6796502564679</v>
       </c>
       <c r="S4">
-        <v>167.4463828994341</v>
+        <v>167.446382899434</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1545,19 +1545,19 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O5">
-        <v>0.5754536981178853</v>
+        <v>0.5754536981178869</v>
       </c>
       <c r="P5">
-        <v>0.8958560122207132</v>
+        <v>0.8958560122207138</v>
       </c>
       <c r="Q5">
-        <v>14.42238148459753</v>
+        <v>14.42238148459756</v>
       </c>
       <c r="R5">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027995</v>
       </c>
       <c r="S5">
-        <v>162.4369087604029</v>
+        <v>162.4369087604028</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1604,19 +1604,19 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O6">
-        <v>0.5754536981178854</v>
+        <v>0.5754536981178868</v>
       </c>
       <c r="P6">
-        <v>0.8958560122207133</v>
+        <v>0.8958560122207138</v>
       </c>
       <c r="Q6">
-        <v>14.42238148459753</v>
+        <v>14.42238148459756</v>
       </c>
       <c r="R6">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027995</v>
       </c>
       <c r="S6">
-        <v>162.4369087604029</v>
+        <v>162.4369087604028</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1663,19 +1663,19 @@
         <v>1.024925070699733</v>
       </c>
       <c r="O7">
-        <v>0.414398598291932</v>
+        <v>0.4143985982919337</v>
       </c>
       <c r="P7">
-        <v>0.9221668923033342</v>
+        <v>0.9221668923033344</v>
       </c>
       <c r="Q7">
-        <v>11.27752546112743</v>
+        <v>11.27752546112745</v>
       </c>
       <c r="R7">
-        <v>-104.6796502252244</v>
+        <v>-104.6796502252243</v>
       </c>
       <c r="S7">
-        <v>167.4463829013833</v>
+        <v>167.4463829013831</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1719,22 +1719,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.085364253680383</v>
+        <v>1.085364253680382</v>
       </c>
       <c r="O8">
-        <v>0.5754536980076312</v>
+        <v>0.5754536980076329</v>
       </c>
       <c r="P8">
-        <v>0.8958560123056806</v>
+        <v>0.8958560123056811</v>
       </c>
       <c r="Q8">
-        <v>14.42238148466651</v>
+        <v>14.42238148466653</v>
       </c>
       <c r="R8">
-        <v>-110.0262110863364</v>
+        <v>-110.0262110863363</v>
       </c>
       <c r="S8">
-        <v>162.4369087636981</v>
+        <v>162.436908763698</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1778,22 +1778,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.085364253680383</v>
+        <v>1.085364253680382</v>
       </c>
       <c r="O9">
-        <v>0.5754536980076315</v>
+        <v>0.5754536980076328</v>
       </c>
       <c r="P9">
-        <v>0.8958560123056805</v>
+        <v>0.8958560123056811</v>
       </c>
       <c r="Q9">
-        <v>14.42238148466651</v>
+        <v>14.42238148466653</v>
       </c>
       <c r="R9">
-        <v>-110.0262110863364</v>
+        <v>-110.0262110863363</v>
       </c>
       <c r="S9">
-        <v>162.4369087636981</v>
+        <v>162.436908763698</v>
       </c>
     </row>
   </sheetData>
@@ -1906,22 +1906,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.105984389062562</v>
+        <v>1.105984389062563</v>
       </c>
       <c r="O2">
-        <v>0.6666637790199428</v>
+        <v>0.666663779019944</v>
       </c>
       <c r="P2">
-        <v>0.9022299634541978</v>
+        <v>0.9022299634542003</v>
       </c>
       <c r="Q2">
-        <v>16.57809355178738</v>
+        <v>16.57809355178737</v>
       </c>
       <c r="R2">
-        <v>-108.7929438266823</v>
+        <v>-108.7929438266821</v>
       </c>
       <c r="S2">
-        <v>159.5275221691293</v>
+        <v>159.5275221691292</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1968,19 +1968,19 @@
         <v>1.085364253791841</v>
       </c>
       <c r="O3">
-        <v>0.5754536980987556</v>
+        <v>0.5754536980987572</v>
       </c>
       <c r="P3">
-        <v>0.8958560121999098</v>
+        <v>0.8958560121999125</v>
       </c>
       <c r="Q3">
-        <v>14.42238148354713</v>
+        <v>14.42238148354711</v>
       </c>
       <c r="R3">
-        <v>-110.0262111070278</v>
+        <v>-110.0262111070276</v>
       </c>
       <c r="S3">
-        <v>162.4369087610724</v>
+        <v>162.4369087610723</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1991,55 +1991,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.172096236067254</v>
+        <v>1.172096236067252</v>
       </c>
       <c r="D4">
-        <v>1.172096236067254</v>
+        <v>1.172096236067252</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>13.53420154819153</v>
+        <v>13.53420154819151</v>
       </c>
       <c r="G4">
-        <v>13.53420154819153</v>
+        <v>13.53420154819151</v>
       </c>
       <c r="H4">
-        <v>5.424025632034072</v>
+        <v>4.144030571481084</v>
       </c>
       <c r="I4">
-        <v>6.488939310918614</v>
+        <v>5.855913331295394</v>
       </c>
       <c r="J4">
-        <v>2.237816431607152</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L4">
-        <v>2.237816431580072</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M4">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>1.024925070816897</v>
+        <v>1.024925070816899</v>
       </c>
       <c r="O4">
-        <v>0.4143985983631078</v>
+        <v>0.4143985983631095</v>
       </c>
       <c r="P4">
-        <v>0.9221668921891045</v>
+        <v>0.922166892189107</v>
       </c>
       <c r="Q4">
-        <v>11.2775254601516</v>
+        <v>11.27752546015159</v>
       </c>
       <c r="R4">
-        <v>-104.679650256468</v>
+        <v>-104.6796502564678</v>
       </c>
       <c r="S4">
-        <v>167.4463828994341</v>
+        <v>167.446382899434</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2086,16 +2086,16 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O5">
-        <v>0.5754536981178862</v>
+        <v>0.5754536981178875</v>
       </c>
       <c r="P5">
-        <v>0.8958560122207123</v>
+        <v>0.8958560122207151</v>
       </c>
       <c r="Q5">
-        <v>14.42238148459757</v>
+        <v>14.42238148459756</v>
       </c>
       <c r="R5">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027994</v>
       </c>
       <c r="S5">
         <v>162.4369087604028</v>
@@ -2145,16 +2145,16 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O6">
-        <v>0.5754536981178862</v>
+        <v>0.5754536981178876</v>
       </c>
       <c r="P6">
-        <v>0.8958560122207124</v>
+        <v>0.8958560122207151</v>
       </c>
       <c r="Q6">
-        <v>14.42238148459757</v>
+        <v>14.42238148459756</v>
       </c>
       <c r="R6">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027994</v>
       </c>
       <c r="S6">
         <v>162.4369087604028</v>
@@ -2201,22 +2201,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.024925070694153</v>
+        <v>1.024925070694154</v>
       </c>
       <c r="O7">
-        <v>0.4143985982885436</v>
+        <v>0.4143985982885454</v>
       </c>
       <c r="P7">
-        <v>0.9221668923087728</v>
+        <v>0.9221668923087752</v>
       </c>
       <c r="Q7">
-        <v>11.27752546117395</v>
+        <v>11.27752546117393</v>
       </c>
       <c r="R7">
-        <v>-104.6796502237366</v>
+        <v>-104.6796502237364</v>
       </c>
       <c r="S7">
-        <v>167.4463829014761</v>
+        <v>167.4463829014759</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.08536425367565</v>
+        <v>1.085364253675651</v>
       </c>
       <c r="O8">
-        <v>0.575453698002382</v>
+        <v>0.5754536980023833</v>
       </c>
       <c r="P8">
-        <v>0.8958560123097259</v>
+        <v>0.8958560123097286</v>
       </c>
       <c r="Q8">
-        <v>14.42238148466984</v>
+        <v>14.42238148466982</v>
       </c>
       <c r="R8">
-        <v>-110.0262110855524</v>
+        <v>-110.0262110855522</v>
       </c>
       <c r="S8">
-        <v>162.436908763855</v>
+        <v>162.4369087638549</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2319,22 +2319,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.08536425367565</v>
+        <v>1.085364253675651</v>
       </c>
       <c r="O9">
-        <v>0.575453698002382</v>
+        <v>0.5754536980023833</v>
       </c>
       <c r="P9">
-        <v>0.8958560123097259</v>
+        <v>0.8958560123097284</v>
       </c>
       <c r="Q9">
-        <v>14.42238148466984</v>
+        <v>14.42238148466982</v>
       </c>
       <c r="R9">
-        <v>-110.0262110855524</v>
+        <v>-110.0262110855522</v>
       </c>
       <c r="S9">
-        <v>162.436908763855</v>
+        <v>162.4369087638549</v>
       </c>
     </row>
   </sheetData>
@@ -2447,22 +2447,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.038230514195722</v>
+        <v>1.03823051419572</v>
       </c>
       <c r="O2">
-        <v>0.4986603516019533</v>
+        <v>0.498660351601954</v>
       </c>
       <c r="P2">
-        <v>0.739194475446264</v>
+        <v>0.7391944754462626</v>
       </c>
       <c r="Q2">
-        <v>10.91142931169907</v>
+        <v>10.9114293116991</v>
       </c>
       <c r="R2">
-        <v>-127.9801517752528</v>
+        <v>-127.9801517752527</v>
       </c>
       <c r="S2">
-        <v>164.5814748093465</v>
+        <v>164.5814748093464</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2506,16 +2506,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9918501269914165</v>
+        <v>0.9918501269914149</v>
       </c>
       <c r="O3">
-        <v>0.3451994260358935</v>
+        <v>0.3451994260358944</v>
       </c>
       <c r="P3">
-        <v>0.7588245169091244</v>
+        <v>0.7588245169091223</v>
       </c>
       <c r="Q3">
-        <v>7.308913743474609</v>
+        <v>7.308913743474657</v>
       </c>
       <c r="R3">
         <v>-133.0240089403622</v>
@@ -2532,49 +2532,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.360220692711321</v>
+        <v>1.360220692711322</v>
       </c>
       <c r="D4">
-        <v>1.360220692711321</v>
+        <v>1.360220692711322</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.70647566188361</v>
+        <v>15.70647566188362</v>
       </c>
       <c r="G4">
-        <v>15.70647566188361</v>
+        <v>15.70647566188362</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.8660254037871229</v>
+        <v>0.8660254037871213</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037860876</v>
+        <v>0.8660254037860857</v>
       </c>
       <c r="Q4">
-        <v>2.956392004144983E-11</v>
+        <v>2.962502395703993E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2624,16 +2624,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9918501269686246</v>
+        <v>0.9918501269686234</v>
       </c>
       <c r="O5">
-        <v>0.3451994260642948</v>
+        <v>0.3451994260642957</v>
       </c>
       <c r="P5">
-        <v>0.7588245169453752</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q5">
-        <v>7.308913746347427</v>
+        <v>7.308913746347478</v>
       </c>
       <c r="R5">
         <v>-133.0240089228248</v>
@@ -2683,16 +2683,16 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9918501269686246</v>
+        <v>0.9918501269686232</v>
       </c>
       <c r="O6">
-        <v>0.3451994260642948</v>
+        <v>0.3451994260642958</v>
       </c>
       <c r="P6">
-        <v>0.7588245169453752</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q6">
-        <v>7.308913746347427</v>
+        <v>7.308913746347471</v>
       </c>
       <c r="R6">
         <v>-133.0240089228248</v>
@@ -2742,16 +2742,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8660254036120051</v>
+        <v>0.8660254036120035</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.8660254039612054</v>
+        <v>0.8660254039612035</v>
       </c>
       <c r="Q7">
-        <v>1.19396498912942E-09</v>
+        <v>1.194021852305561E-09</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2801,22 +2801,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9918501268310793</v>
+        <v>0.9918501268310781</v>
       </c>
       <c r="O8">
-        <v>0.3451994258389098</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P8">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738918</v>
       </c>
       <c r="Q8">
-        <v>7.30891374573073</v>
+        <v>7.30891374573078</v>
       </c>
       <c r="R8">
         <v>-133.0240088964073</v>
       </c>
       <c r="S8">
-        <v>170.4280350620072</v>
+        <v>170.4280350620071</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2860,22 +2860,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9918501268310793</v>
+        <v>0.9918501268310778</v>
       </c>
       <c r="O9">
-        <v>0.3451994258389099</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P9">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738916</v>
       </c>
       <c r="Q9">
-        <v>7.30891374573073</v>
+        <v>7.308913745730774</v>
       </c>
       <c r="R9">
         <v>-133.0240088964073</v>
       </c>
       <c r="S9">
-        <v>170.4280350620072</v>
+        <v>170.4280350620071</v>
       </c>
     </row>
   </sheetData>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.038230514195722</v>
+        <v>1.03823051419572</v>
       </c>
       <c r="O2">
-        <v>0.4986603516019533</v>
+        <v>0.498660351601954</v>
       </c>
       <c r="P2">
-        <v>0.739194475446264</v>
+        <v>0.7391944754462626</v>
       </c>
       <c r="Q2">
-        <v>10.91142931169907</v>
+        <v>10.9114293116991</v>
       </c>
       <c r="R2">
-        <v>-127.9801517752528</v>
+        <v>-127.9801517752527</v>
       </c>
       <c r="S2">
-        <v>164.5814748093465</v>
+        <v>164.5814748093464</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3047,16 +3047,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9918501269914165</v>
+        <v>0.9918501269914149</v>
       </c>
       <c r="O3">
-        <v>0.3451994260358935</v>
+        <v>0.3451994260358944</v>
       </c>
       <c r="P3">
-        <v>0.7588245169091244</v>
+        <v>0.7588245169091223</v>
       </c>
       <c r="Q3">
-        <v>7.308913743474609</v>
+        <v>7.308913743474657</v>
       </c>
       <c r="R3">
         <v>-133.0240089403622</v>
@@ -3073,49 +3073,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.360220692711321</v>
+        <v>1.360220692711322</v>
       </c>
       <c r="D4">
-        <v>1.360220692711321</v>
+        <v>1.360220692711322</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.70647566188361</v>
+        <v>15.70647566188362</v>
       </c>
       <c r="G4">
-        <v>15.70647566188361</v>
+        <v>15.70647566188362</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.8660254037871229</v>
+        <v>0.8660254037871213</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037860876</v>
+        <v>0.8660254037860857</v>
       </c>
       <c r="Q4">
-        <v>2.956392004144983E-11</v>
+        <v>2.962502395703993E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -3165,16 +3165,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9918501269686246</v>
+        <v>0.9918501269686234</v>
       </c>
       <c r="O5">
-        <v>0.3451994260642948</v>
+        <v>0.3451994260642957</v>
       </c>
       <c r="P5">
-        <v>0.7588245169453752</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q5">
-        <v>7.308913746347427</v>
+        <v>7.308913746347478</v>
       </c>
       <c r="R5">
         <v>-133.0240089228248</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9918501269686246</v>
+        <v>0.9918501269686232</v>
       </c>
       <c r="O6">
-        <v>0.3451994260642948</v>
+        <v>0.3451994260642958</v>
       </c>
       <c r="P6">
-        <v>0.7588245169453752</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q6">
-        <v>7.308913746347427</v>
+        <v>7.308913746347471</v>
       </c>
       <c r="R6">
         <v>-133.0240089228248</v>
@@ -3283,16 +3283,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8660254036120051</v>
+        <v>0.8660254036120035</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.8660254039612054</v>
+        <v>0.8660254039612035</v>
       </c>
       <c r="Q7">
-        <v>1.19396498912942E-09</v>
+        <v>1.194021852305561E-09</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3342,22 +3342,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9918501268310793</v>
+        <v>0.9918501268310781</v>
       </c>
       <c r="O8">
-        <v>0.3451994258389098</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P8">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738918</v>
       </c>
       <c r="Q8">
-        <v>7.30891374573073</v>
+        <v>7.30891374573078</v>
       </c>
       <c r="R8">
         <v>-133.0240088964073</v>
       </c>
       <c r="S8">
-        <v>170.4280350620072</v>
+        <v>170.4280350620071</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3401,22 +3401,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9918501268310793</v>
+        <v>0.9918501268310778</v>
       </c>
       <c r="O9">
-        <v>0.3451994258389099</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P9">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738916</v>
       </c>
       <c r="Q9">
-        <v>7.30891374573073</v>
+        <v>7.308913745730774</v>
       </c>
       <c r="R9">
         <v>-133.0240088964073</v>
       </c>
       <c r="S9">
-        <v>170.4280350620072</v>
+        <v>170.4280350620071</v>
       </c>
     </row>
   </sheetData>
@@ -3529,22 +3529,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.029673615020864</v>
+        <v>1.029673615020863</v>
       </c>
       <c r="O2">
-        <v>0.6485080549983552</v>
+        <v>0.6485080549983557</v>
       </c>
       <c r="P2">
-        <v>0.8062590124977642</v>
+        <v>0.8062590124977633</v>
       </c>
       <c r="Q2">
-        <v>17.04738134898281</v>
+        <v>17.04738134898284</v>
       </c>
       <c r="R2">
         <v>-111.4179003643405</v>
       </c>
       <c r="S2">
-        <v>158.0129004047472</v>
+        <v>158.0129004047471</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3588,16 +3588,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9961841591909968</v>
+        <v>0.9961841591909961</v>
       </c>
       <c r="O3">
-        <v>0.5414739855997082</v>
+        <v>0.5414739855997088</v>
       </c>
       <c r="P3">
-        <v>0.8088350632376625</v>
+        <v>0.8088350632376611</v>
       </c>
       <c r="Q3">
-        <v>14.68424123844327</v>
+        <v>14.6842412384433</v>
       </c>
       <c r="R3">
         <v>-111.1354923877622</v>
@@ -3614,10 +3614,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.9232902733308268</v>
+        <v>0.9232902733308271</v>
       </c>
       <c r="D4">
-        <v>0.9232902733308268</v>
+        <v>0.9232902733308271</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3629,37 +3629,37 @@
         <v>10.66123775695432</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.9044714421388741</v>
+        <v>0.9044714421388732</v>
       </c>
       <c r="O4">
-        <v>0.326432406638693</v>
+        <v>0.3264324066386936</v>
       </c>
       <c r="P4">
-        <v>0.8574441488588769</v>
+        <v>0.8574441488588755</v>
       </c>
       <c r="Q4">
-        <v>10.28278020653306</v>
+        <v>10.2827802065331</v>
       </c>
       <c r="R4">
-        <v>-98.42695597435443</v>
+        <v>-98.42695597435448</v>
       </c>
       <c r="S4">
         <v>169.1465925796016</v>
@@ -3706,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O5">
-        <v>0.5414739856400395</v>
+        <v>0.5414739856400402</v>
       </c>
       <c r="P5">
-        <v>0.8088350632677662</v>
+        <v>0.8088350632677648</v>
       </c>
       <c r="Q5">
-        <v>14.68424124043325</v>
+        <v>14.6842412404333</v>
       </c>
       <c r="R5">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S5">
         <v>161.8076671101219</v>
@@ -3765,19 +3765,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O6">
-        <v>0.5414739856400395</v>
+        <v>0.5414739856400401</v>
       </c>
       <c r="P6">
-        <v>0.8088350632677662</v>
+        <v>0.8088350632677648</v>
       </c>
       <c r="Q6">
-        <v>14.68424124043325</v>
+        <v>14.68424124043329</v>
       </c>
       <c r="R6">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S6">
         <v>161.8076671101219</v>
@@ -3824,19 +3824,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9044714420220109</v>
+        <v>0.90447144202201</v>
       </c>
       <c r="O7">
-        <v>0.3264324066106959</v>
+        <v>0.3264324066106967</v>
       </c>
       <c r="P7">
-        <v>0.8574441489768203</v>
+        <v>0.8574441489768189</v>
       </c>
       <c r="Q7">
-        <v>10.28278020810398</v>
+        <v>10.28278020810403</v>
       </c>
       <c r="R7">
-        <v>-98.42695593270598</v>
+        <v>-98.42695593270604</v>
       </c>
       <c r="S7">
         <v>169.1465925808718</v>
@@ -3883,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9961841590838892</v>
+        <v>0.9961841590838886</v>
       </c>
       <c r="O8">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275265</v>
       </c>
       <c r="P8">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454167</v>
       </c>
       <c r="Q8">
-        <v>14.68424124032946</v>
+        <v>14.68424124032951</v>
       </c>
       <c r="R8">
         <v>-111.1354923653206</v>
@@ -3942,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9961841590838892</v>
+        <v>0.9961841590838886</v>
       </c>
       <c r="O9">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275263</v>
       </c>
       <c r="P9">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454167</v>
       </c>
       <c r="Q9">
-        <v>14.68424124032946</v>
+        <v>14.6842412403295</v>
       </c>
       <c r="R9">
         <v>-111.1354923653206</v>
@@ -4070,22 +4070,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.029673615020864</v>
+        <v>1.029673615020863</v>
       </c>
       <c r="O2">
-        <v>0.6485080549983552</v>
+        <v>0.6485080549983557</v>
       </c>
       <c r="P2">
-        <v>0.8062590124977642</v>
+        <v>0.8062590124977633</v>
       </c>
       <c r="Q2">
-        <v>17.04738134898281</v>
+        <v>17.04738134898284</v>
       </c>
       <c r="R2">
         <v>-111.4179003643405</v>
       </c>
       <c r="S2">
-        <v>158.0129004047472</v>
+        <v>158.0129004047471</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -4129,16 +4129,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9961841591909968</v>
+        <v>0.9961841591909961</v>
       </c>
       <c r="O3">
-        <v>0.5414739855997082</v>
+        <v>0.5414739855997088</v>
       </c>
       <c r="P3">
-        <v>0.8088350632376625</v>
+        <v>0.8088350632376611</v>
       </c>
       <c r="Q3">
-        <v>14.68424123844327</v>
+        <v>14.6842412384433</v>
       </c>
       <c r="R3">
         <v>-111.1354923877622</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.9232902733308268</v>
+        <v>0.9232902733308271</v>
       </c>
       <c r="D4">
-        <v>0.9232902733308268</v>
+        <v>0.9232902733308271</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -4170,37 +4170,37 @@
         <v>10.66123775695432</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.9044714421388741</v>
+        <v>0.9044714421388732</v>
       </c>
       <c r="O4">
-        <v>0.326432406638693</v>
+        <v>0.3264324066386936</v>
       </c>
       <c r="P4">
-        <v>0.8574441488588769</v>
+        <v>0.8574441488588755</v>
       </c>
       <c r="Q4">
-        <v>10.28278020653306</v>
+        <v>10.2827802065331</v>
       </c>
       <c r="R4">
-        <v>-98.42695597435443</v>
+        <v>-98.42695597435448</v>
       </c>
       <c r="S4">
         <v>169.1465925796016</v>
@@ -4247,19 +4247,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O5">
-        <v>0.5414739856400395</v>
+        <v>0.5414739856400402</v>
       </c>
       <c r="P5">
-        <v>0.8088350632677662</v>
+        <v>0.8088350632677648</v>
       </c>
       <c r="Q5">
-        <v>14.68424124043325</v>
+        <v>14.6842412404333</v>
       </c>
       <c r="R5">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S5">
         <v>161.8076671101219</v>
@@ -4306,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O6">
-        <v>0.5414739856400395</v>
+        <v>0.5414739856400401</v>
       </c>
       <c r="P6">
-        <v>0.8088350632677662</v>
+        <v>0.8088350632677648</v>
       </c>
       <c r="Q6">
-        <v>14.68424124043325</v>
+        <v>14.68424124043329</v>
       </c>
       <c r="R6">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S6">
         <v>161.8076671101219</v>
@@ -4365,19 +4365,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9044714420220109</v>
+        <v>0.90447144202201</v>
       </c>
       <c r="O7">
-        <v>0.3264324066106959</v>
+        <v>0.3264324066106967</v>
       </c>
       <c r="P7">
-        <v>0.8574441489768203</v>
+        <v>0.8574441489768189</v>
       </c>
       <c r="Q7">
-        <v>10.28278020810398</v>
+        <v>10.28278020810403</v>
       </c>
       <c r="R7">
-        <v>-98.42695593270598</v>
+        <v>-98.42695593270604</v>
       </c>
       <c r="S7">
         <v>169.1465925808718</v>
@@ -4424,16 +4424,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9961841590838892</v>
+        <v>0.9961841590838886</v>
       </c>
       <c r="O8">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275265</v>
       </c>
       <c r="P8">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454167</v>
       </c>
       <c r="Q8">
-        <v>14.68424124032946</v>
+        <v>14.68424124032951</v>
       </c>
       <c r="R8">
         <v>-111.1354923653206</v>
@@ -4483,16 +4483,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9961841590838892</v>
+        <v>0.9961841590838886</v>
       </c>
       <c r="O9">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275263</v>
       </c>
       <c r="P9">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454167</v>
       </c>
       <c r="Q9">
-        <v>14.68424124032946</v>
+        <v>14.6842412403295</v>
       </c>
       <c r="R9">
         <v>-111.1354923653206</v>
@@ -4614,22 +4614,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.690704543768849</v>
+        <v>0.6701093554647523</v>
       </c>
       <c r="O2">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P2">
-        <v>0.9165788224953955</v>
+        <v>0.8924054197913458</v>
       </c>
       <c r="Q2">
-        <v>33.87431367069092</v>
+        <v>35.81393605967047</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999666</v>
+        <v>-89.99999999999665</v>
       </c>
       <c r="S2">
-        <v>128.7305819267978</v>
+        <v>127.511662143737</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4676,22 +4676,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6416038458309423</v>
+        <v>0.6230688550461491</v>
       </c>
       <c r="O3">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P3">
-        <v>0.8604910630369526</v>
+        <v>0.8319416047608118</v>
       </c>
       <c r="Q3">
-        <v>38.63048690959413</v>
+        <v>41.37736785042141</v>
       </c>
       <c r="R3">
         <v>-89.99999999999655</v>
       </c>
       <c r="S3">
-        <v>125.6247237392154</v>
+        <v>124.1927576514372</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4702,7 +4702,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.879618138992242</v>
+        <v>1.993736822392635</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>21.70396077041748</v>
+        <v>23.02168982203314</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4720,43 +4720,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>5.424025632034139</v>
+        <v>4.144030571481131</v>
       </c>
       <c r="I4">
-        <v>6.488939310918272</v>
+        <v>5.855913331295038</v>
       </c>
       <c r="J4">
-        <v>2.237816431602246</v>
+        <v>2.237816431602226</v>
       </c>
       <c r="K4">
-        <v>5.601194464517907</v>
+        <v>5.601194464517905</v>
       </c>
       <c r="L4">
-        <v>2.23781643158026</v>
+        <v>2.23781643158025</v>
       </c>
       <c r="M4">
-        <v>5.6011944645177</v>
+        <v>5.601194464517663</v>
       </c>
       <c r="N4">
-        <v>0.616085536883434</v>
+        <v>0.6102204300157396</v>
       </c>
       <c r="O4">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P4">
-        <v>0.7357403471675247</v>
+        <v>0.6988171900027914</v>
       </c>
       <c r="Q4">
-        <v>50.65955129667951</v>
+        <v>54.57987252493232</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999659</v>
       </c>
       <c r="S4">
-        <v>122.061571814924</v>
+        <v>120.4036908160044</v>
       </c>
       <c r="T4">
-        <v>1.879618138992242</v>
+        <v>1.993736822392634</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4800,22 +4800,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6416038458680836</v>
+        <v>0.6230688550857585</v>
       </c>
       <c r="O5">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P5">
-        <v>0.8604910630311051</v>
+        <v>0.8319416047552867</v>
       </c>
       <c r="Q5">
-        <v>38.63048690994288</v>
+        <v>41.37736785047436</v>
       </c>
       <c r="R5">
         <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>125.6247237416714</v>
+        <v>124.1927576541387</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4862,22 +4862,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6416038458680837</v>
+        <v>0.6230688550857585</v>
       </c>
       <c r="O6">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P6">
-        <v>0.8604910630311051</v>
+        <v>0.8319416047552868</v>
       </c>
       <c r="Q6">
-        <v>38.63048690994288</v>
+        <v>41.37736785047436</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S6">
-        <v>125.6247237416714</v>
+        <v>124.1927576541387</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4924,22 +4924,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6160855370266849</v>
+        <v>0.6102204301813783</v>
       </c>
       <c r="O7">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P7">
-        <v>0.7357403470035909</v>
+        <v>0.6988171898302792</v>
       </c>
       <c r="Q7">
-        <v>50.65955130828237</v>
+        <v>54.57987253570564</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999659</v>
       </c>
       <c r="S7">
-        <v>122.0615718223985</v>
+        <v>120.4036908245411</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4986,22 +4986,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6416038459380672</v>
+        <v>0.6230688551733714</v>
       </c>
       <c r="O8">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P8">
-        <v>0.8604910628844717</v>
+        <v>0.831941604600918</v>
       </c>
       <c r="Q8">
-        <v>38.63048692272726</v>
+        <v>41.37736786376646</v>
       </c>
       <c r="R8">
         <v>-89.99999999999655</v>
       </c>
       <c r="S8">
-        <v>125.624723745825</v>
+        <v>124.1927576588802</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5048,22 +5048,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6416038459380673</v>
+        <v>0.6230688551733713</v>
       </c>
       <c r="O9">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P9">
-        <v>0.8604910628844717</v>
+        <v>0.831941604600918</v>
       </c>
       <c r="Q9">
-        <v>38.63048692272725</v>
+        <v>41.37736786376645</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S9">
-        <v>125.624723745825</v>
+        <v>124.1927576588802</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5182,22 +5182,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.6907045437688484</v>
+        <v>0.6701093554647446</v>
       </c>
       <c r="O2">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P2">
-        <v>0.9165788224953982</v>
+        <v>0.8924054197913533</v>
       </c>
       <c r="Q2">
-        <v>33.87431367069071</v>
+        <v>35.81393605966984</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999663</v>
+        <v>-89.99999999999665</v>
       </c>
       <c r="S2">
-        <v>128.7305819267978</v>
+        <v>127.5116621437365</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5244,22 +5244,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6416038458309411</v>
+        <v>0.6230688550461387</v>
       </c>
       <c r="O3">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P3">
-        <v>0.8604910630369558</v>
+        <v>0.8319416047608201</v>
       </c>
       <c r="Q3">
-        <v>38.63048690959389</v>
+        <v>41.37736785042079</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S3">
-        <v>125.6247237392154</v>
+        <v>124.1927576514365</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.879618138992238</v>
+        <v>1.993736822392633</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5279,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>21.70396077041744</v>
+        <v>23.02168982203312</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5288,43 +5288,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>5.424025632034181</v>
+        <v>4.144030571481241</v>
       </c>
       <c r="I4">
-        <v>6.488939310918274</v>
+        <v>5.855913331294975</v>
       </c>
       <c r="J4">
-        <v>2.23781643160227</v>
+        <v>2.23781643160229</v>
       </c>
       <c r="K4">
-        <v>5.601194464517908</v>
+        <v>5.601194464517867</v>
       </c>
       <c r="L4">
-        <v>2.237816431580284</v>
+        <v>2.23781643158031</v>
       </c>
       <c r="M4">
-        <v>5.601194464517699</v>
+        <v>5.60119446451766</v>
       </c>
       <c r="N4">
-        <v>0.6160855368834316</v>
+        <v>0.6102204300157259</v>
       </c>
       <c r="O4">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P4">
-        <v>0.7357403471675282</v>
+        <v>0.6988171900028012</v>
       </c>
       <c r="Q4">
-        <v>50.65955129667926</v>
+        <v>54.57987252493194</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999653</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S4">
-        <v>122.0615718149239</v>
+        <v>120.4036908160035</v>
       </c>
       <c r="T4">
-        <v>1.879618138992238</v>
+        <v>1.993736822392633</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5368,22 +5368,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6416038458680823</v>
+        <v>0.6230688550857481</v>
       </c>
       <c r="O5">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P5">
-        <v>0.8604910630311083</v>
+        <v>0.8319416047552948</v>
       </c>
       <c r="Q5">
-        <v>38.63048690994264</v>
+        <v>41.37736785047376</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999656</v>
       </c>
       <c r="S5">
-        <v>125.6247237416714</v>
+        <v>124.192757654138</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5430,22 +5430,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6416038458680823</v>
+        <v>0.6230688550857481</v>
       </c>
       <c r="O6">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P6">
-        <v>0.8604910630311083</v>
+        <v>0.8319416047552949</v>
       </c>
       <c r="Q6">
-        <v>38.63048690994265</v>
+        <v>41.37736785047376</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S6">
-        <v>125.6247237416714</v>
+        <v>124.192757654138</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5492,22 +5492,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6160855370335041</v>
+        <v>0.6102204301892522</v>
       </c>
       <c r="O7">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P7">
-        <v>0.7357403469957885</v>
+        <v>0.6988171898220741</v>
       </c>
       <c r="Q7">
-        <v>50.65955130883462</v>
+        <v>54.57987253621827</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999652</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S7">
-        <v>122.0615718227544</v>
+        <v>120.4036908249467</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6416038459413983</v>
+        <v>0.6230688551775327</v>
       </c>
       <c r="O8">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P8">
-        <v>0.8604910628774923</v>
+        <v>0.8319416045935752</v>
       </c>
       <c r="Q8">
-        <v>38.6304869233358</v>
+        <v>41.37736786439881</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999652</v>
+        <v>-89.99999999999656</v>
       </c>
       <c r="S8">
-        <v>125.6247237460228</v>
+        <v>124.1927576591053</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5616,22 +5616,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6416038459413983</v>
+        <v>0.6230688551775327</v>
       </c>
       <c r="O9">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P9">
-        <v>0.8604910628774923</v>
+        <v>0.8319416045935754</v>
       </c>
       <c r="Q9">
-        <v>38.6304869233358</v>
+        <v>41.37736786439881</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999652</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S9">
-        <v>125.6247237460228</v>
+        <v>124.1927576591053</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5750,22 +5750,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8960969432761648</v>
+        <v>0.8894917685036033</v>
       </c>
       <c r="O2">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P2">
-        <v>1.018847183336919</v>
+        <v>1.013635477355387</v>
       </c>
       <c r="Q2">
-        <v>29.6393370227132</v>
+        <v>29.84115243563379</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.8572097420366</v>
+        <v>139.567765888999</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5812,22 +5812,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660113609881631</v>
+        <v>0.8588810253359987</v>
       </c>
       <c r="O3">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P3">
-        <v>0.9895984646517587</v>
+        <v>0.983213467965495</v>
       </c>
       <c r="Q3">
-        <v>30.97920348178567</v>
+        <v>31.2757540190857</v>
       </c>
       <c r="R3">
         <v>-89.99999999999649</v>
       </c>
       <c r="S3">
-        <v>138.6148597240779</v>
+        <v>138.2967164729219</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5838,7 +5838,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.9272674540004709</v>
+        <v>0.956936931243072</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10.70716228355902</v>
+        <v>11.04975589701364</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5856,43 +5856,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>5.424025632034139</v>
+        <v>4.144030571481131</v>
       </c>
       <c r="I4">
-        <v>6.488939310918272</v>
+        <v>5.855913331295038</v>
       </c>
       <c r="J4">
-        <v>2.237816431602246</v>
+        <v>2.237816431602226</v>
       </c>
       <c r="K4">
-        <v>5.601194464517907</v>
+        <v>5.601194464517905</v>
       </c>
       <c r="L4">
-        <v>2.23781643158026</v>
+        <v>2.23781643158025</v>
       </c>
       <c r="M4">
-        <v>5.6011944645177</v>
+        <v>5.601194464517663</v>
       </c>
       <c r="N4">
-        <v>0.8321814670359311</v>
+        <v>0.8253241299356194</v>
       </c>
       <c r="O4">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P4">
-        <v>0.9258054222065151</v>
+        <v>0.9171930367293543</v>
       </c>
       <c r="Q4">
-        <v>34.82090261750643</v>
+        <v>35.32680789369961</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999649</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S4">
-        <v>137.5546695821811</v>
+        <v>137.2352165116173</v>
       </c>
       <c r="T4">
-        <v>0.9272674540004708</v>
+        <v>0.956936931243072</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5936,22 +5936,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.866011361005279</v>
+        <v>0.8588810253538069</v>
       </c>
       <c r="O5">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P5">
-        <v>0.9895984646504469</v>
+        <v>0.9832134679643387</v>
       </c>
       <c r="Q5">
-        <v>30.97920348223673</v>
+        <v>31.27575401953007</v>
       </c>
       <c r="R5">
         <v>-89.99999999999649</v>
       </c>
       <c r="S5">
-        <v>138.6148597251419</v>
+        <v>138.2967164740279</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5998,22 +5998,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.866011361005279</v>
+        <v>0.8588810253538069</v>
       </c>
       <c r="O6">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P6">
-        <v>0.9895984646504469</v>
+        <v>0.9832134679643386</v>
       </c>
       <c r="Q6">
-        <v>30.97920348223673</v>
+        <v>31.27575401953007</v>
       </c>
       <c r="R6">
         <v>-89.99999999999649</v>
       </c>
       <c r="S6">
-        <v>138.6148597251419</v>
+        <v>138.2967164740279</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6060,22 +6060,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8321814670756003</v>
+        <v>0.8253241299787153</v>
       </c>
       <c r="O7">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P7">
-        <v>0.9258054221324425</v>
+        <v>0.9171930366535299</v>
       </c>
       <c r="Q7">
-        <v>34.82090262335212</v>
+        <v>35.32680789971021</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999649</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S7">
-        <v>137.554669585734</v>
+        <v>137.2352165153675</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6122,22 +6122,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8660113610193829</v>
+        <v>0.8588810253700443</v>
       </c>
       <c r="O8">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P8">
-        <v>0.9895984645810181</v>
+        <v>0.9832134678930873</v>
       </c>
       <c r="Q8">
-        <v>30.97920348735336</v>
+        <v>31.27575402483257</v>
       </c>
       <c r="R8">
         <v>-89.99999999999649</v>
       </c>
       <c r="S8">
-        <v>138.6148597272766</v>
+        <v>138.2967164762885</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -6184,22 +6184,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.866011361019383</v>
+        <v>0.8588810253700443</v>
       </c>
       <c r="O9">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P9">
-        <v>0.9895984645810179</v>
+        <v>0.9832134678930872</v>
       </c>
       <c r="Q9">
-        <v>30.97920348735336</v>
+        <v>31.27575402483257</v>
       </c>
       <c r="R9">
         <v>-89.99999999999649</v>
       </c>
       <c r="S9">
-        <v>138.6148597272766</v>
+        <v>138.2967164762885</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -6535,22 +6535,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8960969432761643</v>
+        <v>0.8894917685036003</v>
       </c>
       <c r="O2">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P2">
-        <v>1.018847183336919</v>
+        <v>1.013635477355388</v>
       </c>
       <c r="Q2">
-        <v>29.63933702271314</v>
+        <v>29.84115243563367</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.8572097420366</v>
+        <v>139.5677658889988</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6597,22 +6597,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660113609881624</v>
+        <v>0.8588810253359952</v>
       </c>
       <c r="O3">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P3">
-        <v>0.9895984646517595</v>
+        <v>0.9832134679654962</v>
       </c>
       <c r="Q3">
-        <v>30.97920348178561</v>
+        <v>31.27575401908557</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S3">
-        <v>138.6148597240778</v>
+        <v>138.2967164729217</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.9272674540004698</v>
+        <v>0.9569369312430706</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6632,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10.70716228355901</v>
+        <v>11.04975589701362</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6641,43 +6641,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>5.424025632034181</v>
+        <v>4.144030571481241</v>
       </c>
       <c r="I4">
-        <v>6.488939310918274</v>
+        <v>5.855913331294975</v>
       </c>
       <c r="J4">
-        <v>2.23781643160227</v>
+        <v>2.23781643160229</v>
       </c>
       <c r="K4">
-        <v>5.601194464517908</v>
+        <v>5.601194464517867</v>
       </c>
       <c r="L4">
-        <v>2.237816431580284</v>
+        <v>2.23781643158031</v>
       </c>
       <c r="M4">
-        <v>5.601194464517699</v>
+        <v>5.60119446451766</v>
       </c>
       <c r="N4">
-        <v>0.8321814670359301</v>
+        <v>0.8253241299356152</v>
       </c>
       <c r="O4">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P4">
-        <v>0.925805422206516</v>
+        <v>0.9171930367293555</v>
       </c>
       <c r="Q4">
-        <v>34.82090261750637</v>
+        <v>35.32680789369948</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S4">
-        <v>137.5546695821811</v>
+        <v>137.235216511617</v>
       </c>
       <c r="T4">
-        <v>0.9272674540004697</v>
+        <v>0.9569369312430707</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6721,22 +6721,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8660113610052783</v>
+        <v>0.8588810253538033</v>
       </c>
       <c r="O5">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P5">
-        <v>0.9895984646504477</v>
+        <v>0.9832134679643393</v>
       </c>
       <c r="Q5">
-        <v>30.97920348223667</v>
+        <v>31.27575401952996</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S5">
-        <v>138.6148597251418</v>
+        <v>138.2967164740276</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6783,22 +6783,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8660113610052783</v>
+        <v>0.8588810253538034</v>
       </c>
       <c r="O6">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P6">
-        <v>0.9895984646504477</v>
+        <v>0.9832134679643393</v>
       </c>
       <c r="Q6">
-        <v>30.97920348223668</v>
+        <v>31.27575401952995</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S6">
-        <v>138.6148597251418</v>
+        <v>138.2967164740276</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6845,22 +6845,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8321814670774883</v>
+        <v>0.8253241299807635</v>
       </c>
       <c r="O7">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P7">
-        <v>0.9258054221289163</v>
+        <v>0.9171930366499206</v>
       </c>
       <c r="Q7">
-        <v>34.82090262363042</v>
+        <v>35.32680789999631</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S7">
-        <v>137.5546695859031</v>
+        <v>137.2352165155458</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6907,22 +6907,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.866011361020054</v>
+        <v>0.8588810253708137</v>
       </c>
       <c r="O8">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P8">
-        <v>0.9895984645777126</v>
+        <v>0.9832134678896951</v>
       </c>
       <c r="Q8">
-        <v>30.97920348759695</v>
+        <v>31.27575402508495</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S8">
-        <v>138.6148597273782</v>
+        <v>138.2967164763959</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -6969,22 +6969,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8660113610200537</v>
+        <v>0.8588810253708138</v>
       </c>
       <c r="O9">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P9">
-        <v>0.9895984645777125</v>
+        <v>0.9832134678896952</v>
       </c>
       <c r="Q9">
-        <v>30.97920348759696</v>
+        <v>31.27575402508495</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S9">
-        <v>138.6148597273782</v>
+        <v>138.2967164763959</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7103,22 +7103,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.6768777152300798</v>
+        <v>0.6464421203948201</v>
       </c>
       <c r="O2">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P2">
-        <v>0.9227238885629322</v>
+        <v>0.9012412667911194</v>
       </c>
       <c r="Q2">
-        <v>26.62782469006527</v>
+        <v>27.93372820618389</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999672</v>
+        <v>-89.99999999999669</v>
       </c>
       <c r="S2">
-        <v>130.9773355386828</v>
+        <v>129.3243369262347</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7165,22 +7165,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6239309251876199</v>
+        <v>0.5943943024931746</v>
       </c>
       <c r="O3">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P3">
-        <v>0.8596331470163231</v>
+        <v>0.8315820218503908</v>
       </c>
       <c r="Q3">
-        <v>31.4092856203885</v>
+        <v>33.8265702131776</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S3">
-        <v>128.2763463929966</v>
+        <v>126.4259041360176</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15.09097960701049</v>
+        <v>16.38495748041872</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -7209,43 +7209,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10.07160052780018</v>
+        <v>7.614010012989936</v>
       </c>
       <c r="I4">
-        <v>7.079996444822221</v>
+        <v>6.446970466440814</v>
       </c>
       <c r="J4">
-        <v>3.953518728204021</v>
+        <v>3.953518728204047</v>
       </c>
       <c r="K4">
-        <v>6.198216755313587</v>
+        <v>6.198216755313542</v>
       </c>
       <c r="L4">
-        <v>3.953518728224332</v>
+        <v>3.953518728224348</v>
       </c>
       <c r="M4">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N4">
-        <v>0.5717545054532649</v>
+        <v>0.5587311830649455</v>
       </c>
       <c r="O4">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P4">
-        <v>0.7047630704879301</v>
+        <v>0.6620730627524534</v>
       </c>
       <c r="Q4">
-        <v>46.55389845206195</v>
+        <v>51.4427622661908</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S4">
-        <v>123.9099281709561</v>
+        <v>121.736051118476</v>
       </c>
       <c r="T4">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7289,22 +7289,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.623930925239268</v>
+        <v>0.5943943025500217</v>
       </c>
       <c r="O5">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P5">
-        <v>0.8596331470128098</v>
+        <v>0.8315820218479503</v>
       </c>
       <c r="Q5">
-        <v>31.40928562128463</v>
+        <v>33.82657021366184</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S5">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.623930925239268</v>
+        <v>0.5943943025500216</v>
       </c>
       <c r="O6">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P6">
-        <v>0.8596331470128098</v>
+        <v>0.8315820218479503</v>
       </c>
       <c r="Q6">
-        <v>31.40928562128463</v>
+        <v>33.82657021366185</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S6">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7413,22 +7413,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.5717545055666682</v>
+        <v>0.5587311832060778</v>
       </c>
       <c r="O7">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P7">
-        <v>0.7047630703407078</v>
+        <v>0.6620730625943031</v>
       </c>
       <c r="Q7">
-        <v>46.55389846463247</v>
+        <v>51.4427622782336</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S7">
-        <v>123.9099281777197</v>
+        <v>121.7360511265472</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -7475,22 +7475,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6239309252611086</v>
+        <v>0.5943943025875941</v>
       </c>
       <c r="O8">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P8">
-        <v>0.859633146885618</v>
+        <v>0.8315820217108697</v>
       </c>
       <c r="Q8">
-        <v>31.40928563329063</v>
+        <v>33.82657022705357</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S8">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6239309252611086</v>
+        <v>0.594394302587594</v>
       </c>
       <c r="O9">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P9">
-        <v>0.8596331468856179</v>
+        <v>0.8315820217108697</v>
       </c>
       <c r="Q9">
-        <v>31.40928563329063</v>
+        <v>33.82657022705357</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S9">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7671,22 +7671,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.6768777152300798</v>
+        <v>0.6464421203948201</v>
       </c>
       <c r="O2">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P2">
-        <v>0.9227238885629322</v>
+        <v>0.9012412667911194</v>
       </c>
       <c r="Q2">
-        <v>26.62782469006527</v>
+        <v>27.93372820618389</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999672</v>
+        <v>-89.99999999999669</v>
       </c>
       <c r="S2">
-        <v>130.9773355386828</v>
+        <v>129.3243369262347</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7733,22 +7733,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6239309251876199</v>
+        <v>0.5943943024931746</v>
       </c>
       <c r="O3">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P3">
-        <v>0.8596331470163231</v>
+        <v>0.8315820218503908</v>
       </c>
       <c r="Q3">
-        <v>31.4092856203885</v>
+        <v>33.8265702131776</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S3">
-        <v>128.2763463929966</v>
+        <v>126.4259041360176</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7759,7 +7759,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7768,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15.09097960701049</v>
+        <v>16.38495748041872</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -7777,43 +7777,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10.07160052780018</v>
+        <v>7.614010012989936</v>
       </c>
       <c r="I4">
-        <v>7.079996444822221</v>
+        <v>6.446970466440814</v>
       </c>
       <c r="J4">
-        <v>3.953518728204021</v>
+        <v>3.953518728204047</v>
       </c>
       <c r="K4">
-        <v>6.198216755313587</v>
+        <v>6.198216755313542</v>
       </c>
       <c r="L4">
-        <v>3.953518728224332</v>
+        <v>3.953518728224348</v>
       </c>
       <c r="M4">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N4">
-        <v>0.5717545054532649</v>
+        <v>0.5587311830649455</v>
       </c>
       <c r="O4">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P4">
-        <v>0.7047630704879301</v>
+        <v>0.6620730627524534</v>
       </c>
       <c r="Q4">
-        <v>46.55389845206195</v>
+        <v>51.4427622661908</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S4">
-        <v>123.9099281709561</v>
+        <v>121.736051118476</v>
       </c>
       <c r="T4">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7857,22 +7857,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.623930925239268</v>
+        <v>0.5943943025500217</v>
       </c>
       <c r="O5">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P5">
-        <v>0.8596331470128098</v>
+        <v>0.8315820218479503</v>
       </c>
       <c r="Q5">
-        <v>31.40928562128463</v>
+        <v>33.82657021366184</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S5">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7919,22 +7919,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.623930925239268</v>
+        <v>0.5943943025500216</v>
       </c>
       <c r="O6">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P6">
-        <v>0.8596331470128098</v>
+        <v>0.8315820218479503</v>
       </c>
       <c r="Q6">
-        <v>31.40928562128463</v>
+        <v>33.82657021366185</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S6">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7981,22 +7981,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.5717545055666682</v>
+        <v>0.5587311832060778</v>
       </c>
       <c r="O7">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P7">
-        <v>0.7047630703407078</v>
+        <v>0.6620730625943031</v>
       </c>
       <c r="Q7">
-        <v>46.55389846463247</v>
+        <v>51.4427622782336</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S7">
-        <v>123.9099281777197</v>
+        <v>121.7360511265472</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8043,22 +8043,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6239309252611086</v>
+        <v>0.5943943025875941</v>
       </c>
       <c r="O8">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P8">
-        <v>0.859633146885618</v>
+        <v>0.8315820217108697</v>
       </c>
       <c r="Q8">
-        <v>31.40928563329063</v>
+        <v>33.82657022705357</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S8">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -8105,22 +8105,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6239309252611086</v>
+        <v>0.594394302587594</v>
       </c>
       <c r="O9">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P9">
-        <v>0.8596331468856179</v>
+        <v>0.8315820217108697</v>
       </c>
       <c r="Q9">
-        <v>31.40928563329063</v>
+        <v>33.82657022705357</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S9">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8239,22 +8239,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8206450410105193</v>
+        <v>0.8114013258510477</v>
       </c>
       <c r="O2">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P2">
-        <v>0.947129695925545</v>
+        <v>0.9399771496357334</v>
       </c>
       <c r="Q2">
-        <v>28.23211870828506</v>
+        <v>28.51930871185778</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.7630782572945</v>
+        <v>139.3293505030176</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7908599827081786</v>
+        <v>0.7813661795563565</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P3">
-        <v>0.9090010072409083</v>
+        <v>0.8996640132793633</v>
       </c>
       <c r="Q3">
-        <v>30.34848109574179</v>
+        <v>30.84063589229961</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S3">
-        <v>138.6605985173646</v>
+        <v>138.2191472247096</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8327,7 +8327,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.7260792121740363</v>
+        <v>0.7601192823969949</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8336,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8.384040572033424</v>
+        <v>8.777101446162604</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -8345,43 +8345,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10.07160052780018</v>
+        <v>7.614010012989936</v>
       </c>
       <c r="I4">
-        <v>7.079996444822221</v>
+        <v>6.446970466440814</v>
       </c>
       <c r="J4">
-        <v>3.953518728204021</v>
+        <v>3.953518728204047</v>
       </c>
       <c r="K4">
-        <v>6.198216755313587</v>
+        <v>6.198216755313542</v>
       </c>
       <c r="L4">
-        <v>3.953518728224332</v>
+        <v>3.953518728224348</v>
       </c>
       <c r="M4">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N4">
-        <v>0.7522822461222174</v>
+        <v>0.7447096558032441</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993537</v>
       </c>
       <c r="P4">
-        <v>0.8182764246144573</v>
+        <v>0.8043344692417759</v>
       </c>
       <c r="Q4">
-        <v>36.5664944854173</v>
+        <v>37.54547206386086</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S4">
-        <v>137.5944890480837</v>
+        <v>137.2307998938136</v>
       </c>
       <c r="T4">
-        <v>0.7260792121740361</v>
+        <v>0.7601192823969949</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8425,22 +8425,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.790859982736657</v>
+        <v>0.7813661795864049</v>
       </c>
       <c r="O5">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P5">
-        <v>0.9090010072437242</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q5">
-        <v>30.3484810962097</v>
+        <v>30.8406358927121</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S5">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8487,22 +8487,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7908599827366569</v>
+        <v>0.7813661795864048</v>
       </c>
       <c r="O6">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P6">
-        <v>0.909001007243724</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q6">
-        <v>30.34848109620971</v>
+        <v>30.8406358927121</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S6">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8549,22 +8549,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7522822461707578</v>
+        <v>0.7447096558579159</v>
       </c>
       <c r="O7">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P7">
-        <v>0.8182764245447913</v>
+        <v>0.8043344691703823</v>
       </c>
       <c r="Q7">
-        <v>36.56649449154357</v>
+        <v>37.54547207015098</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S7">
-        <v>137.5944890524971</v>
+        <v>137.2307998986324</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8611,22 +8611,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O8">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P8">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142529</v>
       </c>
       <c r="Q8">
-        <v>30.34848110150038</v>
+        <v>30.84063589828641</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S8">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -8673,22 +8673,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O9">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P9">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142529</v>
       </c>
       <c r="Q9">
-        <v>30.34848110150038</v>
+        <v>30.84063589828641</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S9">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8206450410105193</v>
+        <v>0.8114013258510477</v>
       </c>
       <c r="O2">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P2">
-        <v>0.947129695925545</v>
+        <v>0.9399771496357334</v>
       </c>
       <c r="Q2">
-        <v>28.23211870828506</v>
+        <v>28.51930871185778</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.7630782572945</v>
+        <v>139.3293505030176</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8869,22 +8869,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7908599827081786</v>
+        <v>0.7813661795563565</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P3">
-        <v>0.9090010072409083</v>
+        <v>0.8996640132793633</v>
       </c>
       <c r="Q3">
-        <v>30.34848109574179</v>
+        <v>30.84063589229961</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S3">
-        <v>138.6605985173646</v>
+        <v>138.2191472247096</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.7260792121740363</v>
+        <v>0.7601192823969949</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8904,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8.384040572033424</v>
+        <v>8.777101446162604</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -8913,43 +8913,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10.07160052780018</v>
+        <v>7.614010012989936</v>
       </c>
       <c r="I4">
-        <v>7.079996444822221</v>
+        <v>6.446970466440814</v>
       </c>
       <c r="J4">
-        <v>3.953518728204021</v>
+        <v>3.953518728204047</v>
       </c>
       <c r="K4">
-        <v>6.198216755313587</v>
+        <v>6.198216755313542</v>
       </c>
       <c r="L4">
-        <v>3.953518728224332</v>
+        <v>3.953518728224348</v>
       </c>
       <c r="M4">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N4">
-        <v>0.7522822461222174</v>
+        <v>0.7447096558032441</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993537</v>
       </c>
       <c r="P4">
-        <v>0.8182764246144573</v>
+        <v>0.8043344692417759</v>
       </c>
       <c r="Q4">
-        <v>36.5664944854173</v>
+        <v>37.54547206386086</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S4">
-        <v>137.5944890480837</v>
+        <v>137.2307998938136</v>
       </c>
       <c r="T4">
-        <v>0.7260792121740361</v>
+        <v>0.7601192823969949</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8993,22 +8993,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.790859982736657</v>
+        <v>0.7813661795864049</v>
       </c>
       <c r="O5">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P5">
-        <v>0.9090010072437242</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q5">
-        <v>30.3484810962097</v>
+        <v>30.8406358927121</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S5">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9055,22 +9055,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7908599827366569</v>
+        <v>0.7813661795864048</v>
       </c>
       <c r="O6">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P6">
-        <v>0.909001007243724</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q6">
-        <v>30.34848109620971</v>
+        <v>30.8406358927121</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S6">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9117,22 +9117,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7522822461707578</v>
+        <v>0.7447096558579159</v>
       </c>
       <c r="O7">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P7">
-        <v>0.8182764245447913</v>
+        <v>0.8043344691703823</v>
       </c>
       <c r="Q7">
-        <v>36.56649449154357</v>
+        <v>37.54547207015098</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S7">
-        <v>137.5944890524971</v>
+        <v>137.2307998986324</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9179,22 +9179,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O8">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P8">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142529</v>
       </c>
       <c r="Q8">
-        <v>30.34848110150038</v>
+        <v>30.84063589828641</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S8">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -9241,22 +9241,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O9">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P9">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142529</v>
       </c>
       <c r="Q9">
-        <v>30.34848110150038</v>
+        <v>30.84063589828641</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S9">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9375,22 +9375,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9060616641989658</v>
+        <v>0.8802988101850702</v>
       </c>
       <c r="O2">
-        <v>0.3968725684449336</v>
+        <v>0.396872568444967</v>
       </c>
       <c r="P2">
-        <v>0.7271941441000128</v>
+        <v>0.7024566547428752</v>
       </c>
       <c r="Q2">
-        <v>4.67059765031967</v>
+        <v>4.894674322249265</v>
       </c>
       <c r="R2">
-        <v>-124.0274590209861</v>
+        <v>-124.0274590210184</v>
       </c>
       <c r="S2">
-        <v>159.4605285405378</v>
+        <v>158.8192982474765</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9437,22 +9437,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8462647009938122</v>
+        <v>0.8167335474350078</v>
       </c>
       <c r="O3">
-        <v>0.2604212734076202</v>
+        <v>0.2604212734077011</v>
       </c>
       <c r="P3">
-        <v>0.6969936576743089</v>
+        <v>0.6673414233017354</v>
       </c>
       <c r="Q3">
-        <v>0.6639219845173392</v>
+        <v>0.9849394741810585</v>
       </c>
       <c r="R3">
-        <v>-131.9071155624328</v>
+        <v>-131.9071155624883</v>
       </c>
       <c r="S3">
-        <v>164.6924029404973</v>
+        <v>164.3721586849895</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9466,58 +9466,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2.176343369257086</v>
+        <v>2.185725172736421</v>
       </c>
       <c r="D4">
-        <v>1.82240063122272</v>
+        <v>1.908616693875303</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25.13024860179272</v>
+        <v>25.23858033707829</v>
       </c>
       <c r="G4">
-        <v>21.04326990015562</v>
+        <v>22.0388072397744</v>
       </c>
       <c r="H4">
-        <v>5.424025632034038</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I4">
-        <v>6.488939310918608</v>
+        <v>5.855913331295392</v>
       </c>
       <c r="J4">
-        <v>2.237816431607135</v>
+        <v>2.237816431607154</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564864</v>
       </c>
       <c r="L4">
-        <v>2.237816431580052</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M4">
-        <v>5.601194464517764</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>0.7090618932008849</v>
+        <v>0.6745794393373513</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7090618931995055</v>
+        <v>0.6745794393356759</v>
       </c>
       <c r="Q4">
-        <v>-4.733513263390644</v>
+        <v>-3.987203435893098</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>175.2664867366652</v>
+        <v>176.0127965641787</v>
       </c>
       <c r="T4">
-        <v>1.676798960853584</v>
+        <v>1.880651520533737</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9561,22 +9561,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8462647009829808</v>
+        <v>0.8167335474266544</v>
       </c>
       <c r="O5">
-        <v>0.2604212734213392</v>
+        <v>0.2604212734214202</v>
       </c>
       <c r="P5">
-        <v>0.696993657709862</v>
+        <v>0.6673414233392775</v>
       </c>
       <c r="Q5">
-        <v>0.6639219873516651</v>
+        <v>0.9849394771707543</v>
       </c>
       <c r="R5">
-        <v>-131.9071155467767</v>
+        <v>-131.9071155468322</v>
       </c>
       <c r="S5">
-        <v>164.6924029399332</v>
+        <v>164.3721586845295</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9623,22 +9623,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8462647009829808</v>
+        <v>0.8167335474266544</v>
       </c>
       <c r="O6">
-        <v>0.2604212734213393</v>
+        <v>0.2604212734214199</v>
       </c>
       <c r="P6">
-        <v>0.696993657709862</v>
+        <v>0.6673414233392775</v>
       </c>
       <c r="Q6">
-        <v>0.6639219873516651</v>
+        <v>0.9849394771707477</v>
       </c>
       <c r="R6">
-        <v>-131.9071155467767</v>
+        <v>-131.9071155468322</v>
       </c>
       <c r="S6">
-        <v>164.6924029399332</v>
+        <v>164.3721586845296</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9685,22 +9685,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7090618929984411</v>
+        <v>0.6745794391402782</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.7090618933656316</v>
+        <v>0.674579439507057</v>
       </c>
       <c r="Q7">
-        <v>-4.733513256441465</v>
+        <v>-3.98720342741677</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>175.2664867430916</v>
+        <v>176.0127965716978</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9747,22 +9747,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8462647008070601</v>
+        <v>0.8167335472536181</v>
       </c>
       <c r="O8">
-        <v>0.2604212731950656</v>
+        <v>0.2604212731951465</v>
       </c>
       <c r="P8">
-        <v>0.696993657815188</v>
+        <v>0.6673414234436644</v>
       </c>
       <c r="Q8">
-        <v>0.6639219911179949</v>
+        <v>0.9849394818216595</v>
       </c>
       <c r="R8">
-        <v>-131.9071155004081</v>
+        <v>-131.9071155004635</v>
       </c>
       <c r="S8">
-        <v>164.6924029492251</v>
+        <v>164.3721586951444</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -9809,22 +9809,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.84626470080706</v>
+        <v>0.8167335472536181</v>
       </c>
       <c r="O9">
-        <v>0.2604212731950657</v>
+        <v>0.2604212731951462</v>
       </c>
       <c r="P9">
-        <v>0.6969936578151877</v>
+        <v>0.6673414234436644</v>
       </c>
       <c r="Q9">
-        <v>0.663921991117995</v>
+        <v>0.9849394818216521</v>
       </c>
       <c r="R9">
-        <v>-131.9071155004081</v>
+        <v>-131.9071155004636</v>
       </c>
       <c r="S9">
-        <v>164.6924029492251</v>
+        <v>164.3721586951444</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9943,22 +9943,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9060616641989658</v>
+        <v>0.8802988101850705</v>
       </c>
       <c r="O2">
-        <v>0.3968725684449344</v>
+        <v>0.3968725684449694</v>
       </c>
       <c r="P2">
-        <v>0.7271941441000126</v>
+        <v>0.7024566547428773</v>
       </c>
       <c r="Q2">
-        <v>4.670597650319698</v>
+        <v>4.89467432224926</v>
       </c>
       <c r="R2">
-        <v>-124.0274590209861</v>
+        <v>-124.0274590210181</v>
       </c>
       <c r="S2">
-        <v>159.4605285405378</v>
+        <v>158.8192982474763</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -10005,22 +10005,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8462647009938122</v>
+        <v>0.8167335474350084</v>
       </c>
       <c r="O3">
-        <v>0.2604212734076209</v>
+        <v>0.2604212734077037</v>
       </c>
       <c r="P3">
-        <v>0.6969936576743083</v>
+        <v>0.6673414233017373</v>
       </c>
       <c r="Q3">
-        <v>0.6639219845173696</v>
+        <v>0.9849394741810519</v>
       </c>
       <c r="R3">
-        <v>-131.9071155624328</v>
+        <v>-131.9071155624876</v>
       </c>
       <c r="S3">
-        <v>164.6924029404973</v>
+        <v>164.3721586849892</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10034,58 +10034,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2.176343369257083</v>
+        <v>2.185725172736423</v>
       </c>
       <c r="D4">
-        <v>1.822400631222719</v>
+        <v>1.908616693875293</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25.13024860179268</v>
+        <v>25.2385803370783</v>
       </c>
       <c r="G4">
-        <v>21.04326990015561</v>
+        <v>22.03880723977428</v>
       </c>
       <c r="H4">
-        <v>5.424025632034072</v>
+        <v>4.144030571481084</v>
       </c>
       <c r="I4">
-        <v>6.488939310918614</v>
+        <v>5.855913331295394</v>
       </c>
       <c r="J4">
-        <v>2.237816431607152</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L4">
-        <v>2.237816431580072</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M4">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>0.7090618932008853</v>
+        <v>0.6745794393373516</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7090618931995054</v>
+        <v>0.6745794393356759</v>
       </c>
       <c r="Q4">
-        <v>-4.733513263390644</v>
+        <v>-3.987203435893099</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>175.2664867366652</v>
+        <v>176.0127965641784</v>
       </c>
       <c r="T4">
-        <v>1.676798960853571</v>
+        <v>1.880651520533746</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -10129,22 +10129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8462647009829808</v>
+        <v>0.8167335474266546</v>
       </c>
       <c r="O5">
-        <v>0.2604212734213399</v>
+        <v>0.2604212734214227</v>
       </c>
       <c r="P5">
-        <v>0.6969936577098613</v>
+        <v>0.6673414233392788</v>
       </c>
       <c r="Q5">
-        <v>0.6639219873516928</v>
+        <v>0.9849394771707347</v>
       </c>
       <c r="R5">
-        <v>-131.9071155467767</v>
+        <v>-131.9071155468317</v>
       </c>
       <c r="S5">
-        <v>164.6924029399332</v>
+        <v>164.3721586845292</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10191,22 +10191,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8462647009829808</v>
+        <v>0.8167335474266545</v>
       </c>
       <c r="O6">
-        <v>0.2604212734213399</v>
+        <v>0.2604212734214226</v>
       </c>
       <c r="P6">
-        <v>0.6969936577098612</v>
+        <v>0.6673414233392788</v>
       </c>
       <c r="Q6">
-        <v>0.6639219873516928</v>
+        <v>0.9849394771707309</v>
       </c>
       <c r="R6">
-        <v>-131.9071155467767</v>
+        <v>-131.9071155468316</v>
       </c>
       <c r="S6">
-        <v>164.6924029399332</v>
+        <v>164.3721586845292</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -10253,22 +10253,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7090618929888015</v>
+        <v>0.6745794391308939</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.7090618933735422</v>
+        <v>0.6745794395152179</v>
       </c>
       <c r="Q7">
-        <v>-4.733513256110543</v>
+        <v>-3.987203427013137</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>175.2664867433976</v>
+        <v>176.0127965720555</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10315,22 +10315,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.846264700798683</v>
+        <v>0.8167335472453786</v>
       </c>
       <c r="O8">
-        <v>0.2604212731842914</v>
+        <v>0.2604212731843741</v>
       </c>
       <c r="P8">
-        <v>0.6969936578202027</v>
+        <v>0.6673414234486366</v>
       </c>
       <c r="Q8">
-        <v>0.6639219912973796</v>
+        <v>0.9849394820431171</v>
       </c>
       <c r="R8">
-        <v>-131.9071154982001</v>
+        <v>-131.907115498255</v>
       </c>
       <c r="S8">
-        <v>164.6924029496676</v>
+        <v>164.3721586956496</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -10377,22 +10377,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.846264700798683</v>
+        <v>0.8167335472453786</v>
       </c>
       <c r="O9">
-        <v>0.2604212731842915</v>
+        <v>0.260421273184374</v>
       </c>
       <c r="P9">
-        <v>0.6969936578202027</v>
+        <v>0.6673414234486366</v>
       </c>
       <c r="Q9">
-        <v>0.6639219912973796</v>
+        <v>0.9849394820431085</v>
       </c>
       <c r="R9">
-        <v>-131.9071154982001</v>
+        <v>-131.907115498255</v>
       </c>
       <c r="S9">
-        <v>164.6924029496676</v>
+        <v>164.3721586956496</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -10511,22 +10511,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.018870157837147</v>
+        <v>1.012333429039879</v>
       </c>
       <c r="O2">
-        <v>0.7899048461973629</v>
+        <v>0.7899048461973294</v>
       </c>
       <c r="P2">
-        <v>0.8974666059493107</v>
+        <v>0.8922470519588951</v>
       </c>
       <c r="Q2">
-        <v>18.93851635663321</v>
+        <v>19.00454113733399</v>
       </c>
       <c r="R2">
-        <v>-103.2140010815882</v>
+        <v>-103.2140010815902</v>
       </c>
       <c r="S2">
-        <v>150.765245248015</v>
+        <v>150.5023805559352</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -10573,22 +10573,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9883550265396279</v>
+        <v>0.9809444270614999</v>
       </c>
       <c r="O3">
-        <v>0.7229340275226226</v>
+        <v>0.7229340275225912</v>
       </c>
       <c r="P3">
-        <v>0.8699180559166262</v>
+        <v>0.8634039464346523</v>
       </c>
       <c r="Q3">
-        <v>17.52889632178974</v>
+        <v>17.63611645241663</v>
       </c>
       <c r="R3">
-        <v>-103.7857893953951</v>
+        <v>-103.7857893953976</v>
       </c>
       <c r="S3">
-        <v>152.2959209918941</v>
+        <v>152.0324806142833</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10602,58 +10602,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.9981927965818105</v>
+        <v>1.001759587253732</v>
       </c>
       <c r="D4">
-        <v>0.9225804714925245</v>
+        <v>0.945156822242371</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>11.52613759619307</v>
+        <v>11.56732334728461</v>
       </c>
       <c r="G4">
-        <v>10.65304167130602</v>
+        <v>10.91373091496088</v>
       </c>
       <c r="H4">
-        <v>5.424025632034038</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I4">
-        <v>6.488939310918608</v>
+        <v>5.855913331295392</v>
       </c>
       <c r="J4">
-        <v>2.237816431607135</v>
+        <v>2.237816431607154</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564864</v>
       </c>
       <c r="L4">
-        <v>2.237816431580052</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M4">
-        <v>5.601194464517764</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>0.920589402939427</v>
+        <v>0.9122451454600227</v>
       </c>
       <c r="O4">
-        <v>0.6059501515843787</v>
+        <v>0.6059501515843448</v>
       </c>
       <c r="P4">
-        <v>0.8427568787084931</v>
+        <v>0.8340298058017078</v>
       </c>
       <c r="Q4">
-        <v>16.20299603543411</v>
+        <v>16.43051994443773</v>
       </c>
       <c r="R4">
-        <v>-100.6772421604384</v>
+        <v>-100.677242160442</v>
       </c>
       <c r="S4">
-        <v>156.3124525110437</v>
+        <v>156.13545329578</v>
       </c>
       <c r="T4">
-        <v>0.8704495857947014</v>
+        <v>0.9253554392383687</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -10697,22 +10697,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9883550265373902</v>
+        <v>0.9809444270598852</v>
       </c>
       <c r="O5">
-        <v>0.7229340275378111</v>
+        <v>0.7229340275377797</v>
       </c>
       <c r="P5">
-        <v>0.8699180559342961</v>
+        <v>0.8634039464526182</v>
       </c>
       <c r="Q5">
-        <v>17.52889632293214</v>
+        <v>17.63611645357536</v>
       </c>
       <c r="R5">
-        <v>-103.7857893929796</v>
+        <v>-103.7857893929821</v>
       </c>
       <c r="S5">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10759,22 +10759,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9883550265373902</v>
+        <v>0.9809444270598852</v>
       </c>
       <c r="O6">
-        <v>0.7229340275378111</v>
+        <v>0.7229340275377796</v>
       </c>
       <c r="P6">
-        <v>0.8699180559342961</v>
+        <v>0.8634039464526181</v>
       </c>
       <c r="Q6">
-        <v>17.52889632293214</v>
+        <v>17.63611645357535</v>
       </c>
       <c r="R6">
-        <v>-103.7857893929796</v>
+        <v>-103.7857893929821</v>
       </c>
       <c r="S6">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -10821,22 +10821,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9205894028569054</v>
+        <v>0.9122451453792305</v>
       </c>
       <c r="O7">
-        <v>0.6059501515323414</v>
+        <v>0.6059501515323075</v>
       </c>
       <c r="P7">
-        <v>0.8427568787572177</v>
+        <v>0.8340298058496108</v>
       </c>
       <c r="Q7">
-        <v>16.2029960390458</v>
+        <v>16.43051994826991</v>
       </c>
       <c r="R7">
-        <v>-100.6772421448166</v>
+        <v>-100.6772421448202</v>
       </c>
       <c r="S7">
-        <v>156.3124525164484</v>
+        <v>156.1354533014574</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10883,22 +10883,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9883550264610569</v>
+        <v>0.9809444269844851</v>
       </c>
       <c r="O8">
-        <v>0.7229340274619847</v>
+        <v>0.7229340274619532</v>
       </c>
       <c r="P8">
-        <v>0.8699180559566703</v>
+        <v>0.863403946473532</v>
       </c>
       <c r="Q8">
-        <v>17.52889632504997</v>
+        <v>17.6361164558582</v>
       </c>
       <c r="R8">
-        <v>-103.7857893831563</v>
+        <v>-103.7857893831588</v>
       </c>
       <c r="S8">
-        <v>152.2959209971515</v>
+        <v>152.0324806197792</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -10945,22 +10945,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9883550264610569</v>
+        <v>0.9809444269844851</v>
       </c>
       <c r="O9">
-        <v>0.7229340274619847</v>
+        <v>0.7229340274619531</v>
       </c>
       <c r="P9">
-        <v>0.8699180559566703</v>
+        <v>0.8634039464735319</v>
       </c>
       <c r="Q9">
-        <v>17.52889632504997</v>
+        <v>17.6361164558582</v>
       </c>
       <c r="R9">
-        <v>-103.7857893831563</v>
+        <v>-103.7857893831588</v>
       </c>
       <c r="S9">
-        <v>152.2959209971515</v>
+        <v>152.0324806197792</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11079,22 +11079,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.018870157837147</v>
+        <v>1.012333429039879</v>
       </c>
       <c r="O2">
-        <v>0.7899048461973636</v>
+        <v>0.7899048461973301</v>
       </c>
       <c r="P2">
-        <v>0.8974666059493104</v>
+        <v>0.8922470519588958</v>
       </c>
       <c r="Q2">
-        <v>18.93851635663323</v>
+        <v>19.00454113733399</v>
       </c>
       <c r="R2">
-        <v>-103.2140010815882</v>
+        <v>-103.2140010815901</v>
       </c>
       <c r="S2">
-        <v>150.765245248015</v>
+        <v>150.5023805559352</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -11141,22 +11141,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9883550265396276</v>
+        <v>0.9809444270615002</v>
       </c>
       <c r="O3">
-        <v>0.7229340275226231</v>
+        <v>0.7229340275225923</v>
       </c>
       <c r="P3">
-        <v>0.8699180559166256</v>
+        <v>0.8634039464346532</v>
       </c>
       <c r="Q3">
-        <v>17.52889632178977</v>
+        <v>17.63611645241663</v>
       </c>
       <c r="R3">
-        <v>-103.7857893953951</v>
+        <v>-103.7857893953976</v>
       </c>
       <c r="S3">
-        <v>152.295920991894</v>
+        <v>152.0324806142833</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11170,58 +11170,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.9981927965818097</v>
+        <v>1.001759587253732</v>
       </c>
       <c r="D4">
-        <v>0.9225804714925245</v>
+        <v>0.9451568222423685</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>11.52613759619306</v>
+        <v>11.56732334728461</v>
       </c>
       <c r="G4">
-        <v>10.65304167130602</v>
+        <v>10.91373091496085</v>
       </c>
       <c r="H4">
-        <v>5.424025632034072</v>
+        <v>4.144030571481084</v>
       </c>
       <c r="I4">
-        <v>6.488939310918614</v>
+        <v>5.855913331295394</v>
       </c>
       <c r="J4">
-        <v>2.237816431607152</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L4">
-        <v>2.237816431580072</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M4">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>0.9205894029394269</v>
+        <v>0.9122451454600229</v>
       </c>
       <c r="O4">
-        <v>0.6059501515843793</v>
+        <v>0.6059501515843463</v>
       </c>
       <c r="P4">
-        <v>0.8427568787084929</v>
+        <v>0.8340298058017086</v>
       </c>
       <c r="Q4">
-        <v>16.20299603543413</v>
+        <v>16.43051994443774</v>
       </c>
       <c r="R4">
-        <v>-100.6772421604384</v>
+        <v>-100.6772421604419</v>
       </c>
       <c r="S4">
-        <v>156.3124525110437</v>
+        <v>156.13545329578</v>
       </c>
       <c r="T4">
-        <v>0.8704495857946981</v>
+        <v>0.9253554392383697</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -11265,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9883550265373899</v>
+        <v>0.9809444270598854</v>
       </c>
       <c r="O5">
-        <v>0.7229340275378118</v>
+        <v>0.7229340275377808</v>
       </c>
       <c r="P5">
-        <v>0.8699180559342955</v>
+        <v>0.863403946452619</v>
       </c>
       <c r="Q5">
-        <v>17.52889632293216</v>
+        <v>17.63611645357536</v>
       </c>
       <c r="R5">
-        <v>-103.7857893929796</v>
+        <v>-103.785789392982</v>
       </c>
       <c r="S5">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11327,22 +11327,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9883550265373899</v>
+        <v>0.9809444270598853</v>
       </c>
       <c r="O6">
-        <v>0.7229340275378118</v>
+        <v>0.7229340275377808</v>
       </c>
       <c r="P6">
-        <v>0.8699180559342955</v>
+        <v>0.8634039464526192</v>
       </c>
       <c r="Q6">
-        <v>17.52889632293216</v>
+        <v>17.63611645357537</v>
       </c>
       <c r="R6">
-        <v>-103.7857893929796</v>
+        <v>-103.785789392982</v>
       </c>
       <c r="S6">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -11389,22 +11389,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9205894028529756</v>
+        <v>0.9122451453753835</v>
       </c>
       <c r="O7">
-        <v>0.6059501515298639</v>
+        <v>0.6059501515298309</v>
       </c>
       <c r="P7">
-        <v>0.8427568787595375</v>
+        <v>0.8340298058518926</v>
       </c>
       <c r="Q7">
-        <v>16.20299603921781</v>
+        <v>16.43051994845241</v>
       </c>
       <c r="R7">
-        <v>-100.6772421440727</v>
+        <v>-100.6772421440762</v>
       </c>
       <c r="S7">
-        <v>156.3124525167057</v>
+        <v>156.1354533017277</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -11451,22 +11451,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9883550264574218</v>
+        <v>0.9809444269808949</v>
       </c>
       <c r="O8">
-        <v>0.7229340274583744</v>
+        <v>0.7229340274583435</v>
       </c>
       <c r="P8">
-        <v>0.8699180559577353</v>
+        <v>0.8634039464745283</v>
       </c>
       <c r="Q8">
-        <v>17.52889632515084</v>
+        <v>17.63611645596691</v>
       </c>
       <c r="R8">
-        <v>-103.7857893826886</v>
+        <v>-103.785789382691</v>
       </c>
       <c r="S8">
-        <v>152.2959209973866</v>
+        <v>152.0324806200236</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -11513,22 +11513,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9883550264574218</v>
+        <v>0.9809444269808949</v>
       </c>
       <c r="O9">
-        <v>0.7229340274583744</v>
+        <v>0.7229340274583432</v>
       </c>
       <c r="P9">
-        <v>0.8699180559577353</v>
+        <v>0.8634039464745283</v>
       </c>
       <c r="Q9">
-        <v>17.52889632515084</v>
+        <v>17.63611645596691</v>
       </c>
       <c r="R9">
-        <v>-103.7857893826886</v>
+        <v>-103.785789382691</v>
       </c>
       <c r="S9">
-        <v>152.2959209973866</v>
+        <v>152.0324806200236</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11647,22 +11647,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.926402659111094</v>
+        <v>0.9008805616346984</v>
       </c>
       <c r="O2">
-        <v>0.4986603516025515</v>
+        <v>0.4986603516026911</v>
       </c>
       <c r="P2">
-        <v>0.6799263258459319</v>
+        <v>0.6601514092604911</v>
       </c>
       <c r="Q2">
-        <v>6.259570784359538</v>
+        <v>6.048271569189423</v>
       </c>
       <c r="R2">
-        <v>-127.9801517751898</v>
+        <v>-127.9801517751726</v>
       </c>
       <c r="S2">
-        <v>154.5623657971338</v>
+        <v>153.1527191485391</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -11709,22 +11709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8545773200093233</v>
+        <v>0.8249241208093135</v>
       </c>
       <c r="O3">
-        <v>0.3451994260363931</v>
+        <v>0.3451994260365134</v>
       </c>
       <c r="P3">
-        <v>0.6550597341008624</v>
+        <v>0.627989237499858</v>
       </c>
       <c r="Q3">
-        <v>2.412928811293917</v>
+        <v>2.343640655781055</v>
       </c>
       <c r="R3">
-        <v>-133.0240089402593</v>
+        <v>-133.0240089402313</v>
       </c>
       <c r="S3">
-        <v>160.7112239499163</v>
+        <v>159.6261613779621</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11738,58 +11738,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.610978819204034</v>
+        <v>1.624700707645011</v>
       </c>
       <c r="D4">
-        <v>1.306941916567834</v>
+        <v>1.371103885022675</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>18.60198109852469</v>
+        <v>18.76042781822845</v>
       </c>
       <c r="G4">
-        <v>15.09126534691289</v>
+        <v>15.83214394209566</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.6759626201272254</v>
+        <v>0.638506588517748</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6759626201265754</v>
+        <v>0.6385065885171641</v>
       </c>
       <c r="Q4">
-        <v>-5.086999826385507</v>
+        <v>-4.610782588584477</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>174.913000173459</v>
+        <v>175.3892174112333</v>
       </c>
       <c r="T4">
-        <v>1.098134111521839</v>
+        <v>1.279982489867892</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -11833,22 +11833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8545773199974886</v>
+        <v>0.8249241208013738</v>
       </c>
       <c r="O5">
-        <v>0.3451994260647945</v>
+        <v>0.3451994260649147</v>
       </c>
       <c r="P5">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540606</v>
       </c>
       <c r="Q5">
-        <v>2.412928815564764</v>
+        <v>2.343640660285834</v>
       </c>
       <c r="R5">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226939</v>
       </c>
       <c r="S5">
-        <v>160.7112239487163</v>
+        <v>159.626161377037</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11895,22 +11895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8545773199974886</v>
+        <v>0.8249241208013739</v>
       </c>
       <c r="O6">
-        <v>0.3451994260647944</v>
+        <v>0.3451994260649149</v>
       </c>
       <c r="P6">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540608</v>
       </c>
       <c r="Q6">
-        <v>2.412928815564765</v>
+        <v>2.343640660285837</v>
       </c>
       <c r="R6">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226939</v>
       </c>
       <c r="S6">
-        <v>160.7112239487163</v>
+        <v>159.6261613770369</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -11957,22 +11957,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6759626199309128</v>
+        <v>0.6385065883253098</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.67596262028224</v>
+        <v>0.6385065886766578</v>
       </c>
       <c r="Q7">
-        <v>-5.08699982044555</v>
+        <v>-4.610782580991185</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>174.9130001790594</v>
+        <v>175.3892174182046</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -12019,22 +12019,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409469</v>
       </c>
       <c r="O8">
-        <v>0.3451994258394096</v>
+        <v>0.3451994258395298</v>
       </c>
       <c r="P8">
-        <v>0.6550597342282263</v>
+        <v>0.627989237625226</v>
       </c>
       <c r="Q8">
-        <v>2.412928817402773</v>
+        <v>2.343640662900233</v>
       </c>
       <c r="R8">
-        <v>-133.0240088963044</v>
+        <v>-133.0240088962763</v>
       </c>
       <c r="S8">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -12081,22 +12081,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409469</v>
       </c>
       <c r="O9">
-        <v>0.3451994258394096</v>
+        <v>0.3451994258395301</v>
       </c>
       <c r="P9">
-        <v>0.6550597342282263</v>
+        <v>0.627989237625226</v>
       </c>
       <c r="Q9">
-        <v>2.412928817402773</v>
+        <v>2.343640662900236</v>
       </c>
       <c r="R9">
-        <v>-133.0240088963044</v>
+        <v>-133.0240088962764</v>
       </c>
       <c r="S9">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -12432,22 +12432,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.926402659111094</v>
+        <v>0.9008805616346984</v>
       </c>
       <c r="O2">
-        <v>0.4986603516025515</v>
+        <v>0.4986603516026911</v>
       </c>
       <c r="P2">
-        <v>0.6799263258459319</v>
+        <v>0.6601514092604911</v>
       </c>
       <c r="Q2">
-        <v>6.259570784359538</v>
+        <v>6.048271569189423</v>
       </c>
       <c r="R2">
-        <v>-127.9801517751898</v>
+        <v>-127.9801517751726</v>
       </c>
       <c r="S2">
-        <v>154.5623657971338</v>
+        <v>153.1527191485391</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -12494,22 +12494,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8545773200093233</v>
+        <v>0.8249241208093135</v>
       </c>
       <c r="O3">
-        <v>0.3451994260363931</v>
+        <v>0.3451994260365134</v>
       </c>
       <c r="P3">
-        <v>0.6550597341008624</v>
+        <v>0.627989237499858</v>
       </c>
       <c r="Q3">
-        <v>2.412928811293917</v>
+        <v>2.343640655781055</v>
       </c>
       <c r="R3">
-        <v>-133.0240089402593</v>
+        <v>-133.0240089402313</v>
       </c>
       <c r="S3">
-        <v>160.7112239499163</v>
+        <v>159.6261613779621</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -12523,58 +12523,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.610978819204034</v>
+        <v>1.624700707645011</v>
       </c>
       <c r="D4">
-        <v>1.306941916567834</v>
+        <v>1.371103885022675</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>18.60198109852469</v>
+        <v>18.76042781822845</v>
       </c>
       <c r="G4">
-        <v>15.09126534691289</v>
+        <v>15.83214394209566</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.6759626201272254</v>
+        <v>0.638506588517748</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6759626201265754</v>
+        <v>0.6385065885171641</v>
       </c>
       <c r="Q4">
-        <v>-5.086999826385507</v>
+        <v>-4.610782588584477</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>174.913000173459</v>
+        <v>175.3892174112333</v>
       </c>
       <c r="T4">
-        <v>1.098134111521839</v>
+        <v>1.279982489867892</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -12618,22 +12618,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8545773199974886</v>
+        <v>0.8249241208013738</v>
       </c>
       <c r="O5">
-        <v>0.3451994260647945</v>
+        <v>0.3451994260649147</v>
       </c>
       <c r="P5">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540606</v>
       </c>
       <c r="Q5">
-        <v>2.412928815564764</v>
+        <v>2.343640660285834</v>
       </c>
       <c r="R5">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226939</v>
       </c>
       <c r="S5">
-        <v>160.7112239487163</v>
+        <v>159.626161377037</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -12680,22 +12680,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8545773199974886</v>
+        <v>0.8249241208013739</v>
       </c>
       <c r="O6">
-        <v>0.3451994260647944</v>
+        <v>0.3451994260649149</v>
       </c>
       <c r="P6">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540608</v>
       </c>
       <c r="Q6">
-        <v>2.412928815564765</v>
+        <v>2.343640660285837</v>
       </c>
       <c r="R6">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226939</v>
       </c>
       <c r="S6">
-        <v>160.7112239487163</v>
+        <v>159.6261613770369</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -12742,22 +12742,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6759626199309128</v>
+        <v>0.6385065883253098</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.67596262028224</v>
+        <v>0.6385065886766578</v>
       </c>
       <c r="Q7">
-        <v>-5.08699982044555</v>
+        <v>-4.610782580991185</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>174.9130001790594</v>
+        <v>175.3892174182046</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -12804,22 +12804,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409469</v>
       </c>
       <c r="O8">
-        <v>0.3451994258394096</v>
+        <v>0.3451994258395298</v>
       </c>
       <c r="P8">
-        <v>0.6550597342282263</v>
+        <v>0.627989237625226</v>
       </c>
       <c r="Q8">
-        <v>2.412928817402773</v>
+        <v>2.343640662900233</v>
       </c>
       <c r="R8">
-        <v>-133.0240088963044</v>
+        <v>-133.0240088962763</v>
       </c>
       <c r="S8">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -12866,22 +12866,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409469</v>
       </c>
       <c r="O9">
-        <v>0.3451994258394096</v>
+        <v>0.3451994258395301</v>
       </c>
       <c r="P9">
-        <v>0.6550597342282263</v>
+        <v>0.627989237625226</v>
       </c>
       <c r="Q9">
-        <v>2.412928817402773</v>
+        <v>2.343640662900236</v>
       </c>
       <c r="R9">
-        <v>-133.0240088963044</v>
+        <v>-133.0240088962764</v>
       </c>
       <c r="S9">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13000,22 +13000,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9481529538720904</v>
+        <v>0.9395756489355315</v>
       </c>
       <c r="O2">
-        <v>0.7322760567500222</v>
+        <v>0.7322760567500916</v>
       </c>
       <c r="P2">
-        <v>0.8195702772728284</v>
+        <v>0.8131326300099632</v>
       </c>
       <c r="Q2">
-        <v>18.35097919590552</v>
+        <v>18.41212906161129</v>
       </c>
       <c r="R2">
-        <v>-105.0054683023685</v>
+        <v>-105.0054683023667</v>
       </c>
       <c r="S2">
-        <v>150.0800940821339</v>
+        <v>149.6760428132002</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -13062,22 +13062,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9063792353652222</v>
+        <v>0.8967513407179984</v>
       </c>
       <c r="O3">
-        <v>0.6518511244466931</v>
+        <v>0.6518511244467626</v>
       </c>
       <c r="P3">
-        <v>0.7957851127118389</v>
+        <v>0.7871653857144369</v>
       </c>
       <c r="Q3">
-        <v>16.9678765633369</v>
+        <v>17.12839440493407</v>
       </c>
       <c r="R3">
-        <v>-104.2907188442087</v>
+        <v>-104.2907188442066</v>
       </c>
       <c r="S3">
-        <v>152.5232317989533</v>
+        <v>152.1628946801794</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13091,58 +13091,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.8172794759706626</v>
+        <v>0.8192909477601666</v>
       </c>
       <c r="D4">
-        <v>0.7217366689642836</v>
+        <v>0.7477476736924514</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>9.437130509096367</v>
+        <v>9.460356984679118</v>
       </c>
       <c r="G4">
-        <v>8.333897202211059</v>
+        <v>8.634246413845066</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.805551848031219</v>
+        <v>0.7946343373671535</v>
       </c>
       <c r="O4">
-        <v>0.4931849650005626</v>
+        <v>0.4931849650006356</v>
       </c>
       <c r="P4">
-        <v>0.7735594206637817</v>
+        <v>0.760928279246093</v>
       </c>
       <c r="Q4">
-        <v>15.34097325496875</v>
+        <v>15.80538487780018</v>
       </c>
       <c r="R4">
-        <v>-96.35596491160985</v>
+        <v>-96.35596491160764</v>
       </c>
       <c r="S4">
-        <v>159.014630398495</v>
+        <v>158.917217550757</v>
       </c>
       <c r="T4">
-        <v>0.657151310375827</v>
+        <v>0.717549443297119</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -13186,22 +13186,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9063792353665443</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O5">
-        <v>0.6518511244809748</v>
+        <v>0.6518511244810441</v>
       </c>
       <c r="P5">
-        <v>0.7957851127408441</v>
+        <v>0.7871653857444232</v>
       </c>
       <c r="Q5">
-        <v>16.96787656541303</v>
+        <v>17.12839440703171</v>
       </c>
       <c r="R5">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403032</v>
       </c>
       <c r="S5">
-        <v>152.5232317990343</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -13248,22 +13248,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9063792353665443</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O6">
-        <v>0.6518511244809748</v>
+        <v>0.6518511244810443</v>
       </c>
       <c r="P6">
-        <v>0.7957851127408441</v>
+        <v>0.7871653857444232</v>
       </c>
       <c r="Q6">
-        <v>16.96787656541303</v>
+        <v>17.12839440703172</v>
       </c>
       <c r="R6">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403032</v>
       </c>
       <c r="S6">
-        <v>152.5232317990343</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -13310,22 +13310,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.805551847948285</v>
+        <v>0.7946343372874242</v>
       </c>
       <c r="O7">
-        <v>0.4931849649794131</v>
+        <v>0.4931849649794862</v>
       </c>
       <c r="P7">
-        <v>0.7735594207261949</v>
+        <v>0.7609282793083719</v>
       </c>
       <c r="Q7">
-        <v>15.34097325963533</v>
+        <v>15.80538488283765</v>
       </c>
       <c r="R7">
-        <v>-96.35596489078564</v>
+        <v>-96.35596489078344</v>
       </c>
       <c r="S7">
-        <v>159.0146304036402</v>
+        <v>158.9172175563322</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13372,22 +13372,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.906379235289956</v>
+        <v>0.8967513406455306</v>
       </c>
       <c r="O8">
-        <v>0.6518511244056875</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P8">
-        <v>0.795785112763417</v>
+        <v>0.787165385765108</v>
       </c>
       <c r="Q8">
-        <v>16.96787656741729</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R8">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S8">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -13434,22 +13434,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.906379235289956</v>
+        <v>0.8967513406455307</v>
       </c>
       <c r="O9">
-        <v>0.6518511244056875</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P9">
-        <v>0.795785112763417</v>
+        <v>0.787165385765108</v>
       </c>
       <c r="Q9">
-        <v>16.96787656741729</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R9">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S9">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13568,22 +13568,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9481529538720904</v>
+        <v>0.9395756489355315</v>
       </c>
       <c r="O2">
-        <v>0.7322760567500222</v>
+        <v>0.7322760567500916</v>
       </c>
       <c r="P2">
-        <v>0.8195702772728284</v>
+        <v>0.8131326300099632</v>
       </c>
       <c r="Q2">
-        <v>18.35097919590552</v>
+        <v>18.41212906161129</v>
       </c>
       <c r="R2">
-        <v>-105.0054683023685</v>
+        <v>-105.0054683023667</v>
       </c>
       <c r="S2">
-        <v>150.0800940821339</v>
+        <v>149.6760428132002</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -13630,22 +13630,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9063792353652222</v>
+        <v>0.8967513407179984</v>
       </c>
       <c r="O3">
-        <v>0.6518511244466931</v>
+        <v>0.6518511244467626</v>
       </c>
       <c r="P3">
-        <v>0.7957851127118389</v>
+        <v>0.7871653857144369</v>
       </c>
       <c r="Q3">
-        <v>16.9678765633369</v>
+        <v>17.12839440493407</v>
       </c>
       <c r="R3">
-        <v>-104.2907188442087</v>
+        <v>-104.2907188442066</v>
       </c>
       <c r="S3">
-        <v>152.5232317989533</v>
+        <v>152.1628946801794</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13659,58 +13659,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.8172794759706626</v>
+        <v>0.8192909477601666</v>
       </c>
       <c r="D4">
-        <v>0.7217366689642836</v>
+        <v>0.7477476736924514</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>9.437130509096367</v>
+        <v>9.460356984679118</v>
       </c>
       <c r="G4">
-        <v>8.333897202211059</v>
+        <v>8.634246413845066</v>
       </c>
       <c r="H4">
-        <v>10.07160052779999</v>
+        <v>7.614010012989714</v>
       </c>
       <c r="I4">
-        <v>7.079996444822625</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J4">
-        <v>3.953518728206193</v>
+        <v>3.953518728206217</v>
       </c>
       <c r="K4">
-        <v>6.198216755282932</v>
+        <v>6.198216755282953</v>
       </c>
       <c r="L4">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M4">
-        <v>6.198216755313508</v>
+        <v>6.198216755313492</v>
       </c>
       <c r="N4">
-        <v>0.805551848031219</v>
+        <v>0.7946343373671535</v>
       </c>
       <c r="O4">
-        <v>0.4931849650005626</v>
+        <v>0.4931849650006356</v>
       </c>
       <c r="P4">
-        <v>0.7735594206637817</v>
+        <v>0.760928279246093</v>
       </c>
       <c r="Q4">
-        <v>15.34097325496875</v>
+        <v>15.80538487780018</v>
       </c>
       <c r="R4">
-        <v>-96.35596491160985</v>
+        <v>-96.35596491160764</v>
       </c>
       <c r="S4">
-        <v>159.014630398495</v>
+        <v>158.917217550757</v>
       </c>
       <c r="T4">
-        <v>0.657151310375827</v>
+        <v>0.717549443297119</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -13754,22 +13754,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9063792353665443</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O5">
-        <v>0.6518511244809748</v>
+        <v>0.6518511244810441</v>
       </c>
       <c r="P5">
-        <v>0.7957851127408441</v>
+        <v>0.7871653857444232</v>
       </c>
       <c r="Q5">
-        <v>16.96787656541303</v>
+        <v>17.12839440703171</v>
       </c>
       <c r="R5">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403032</v>
       </c>
       <c r="S5">
-        <v>152.5232317990343</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -13816,22 +13816,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9063792353665443</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O6">
-        <v>0.6518511244809748</v>
+        <v>0.6518511244810443</v>
       </c>
       <c r="P6">
-        <v>0.7957851127408441</v>
+        <v>0.7871653857444232</v>
       </c>
       <c r="Q6">
-        <v>16.96787656541303</v>
+        <v>17.12839440703172</v>
       </c>
       <c r="R6">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403032</v>
       </c>
       <c r="S6">
-        <v>152.5232317990343</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -13878,22 +13878,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.805551847948285</v>
+        <v>0.7946343372874242</v>
       </c>
       <c r="O7">
-        <v>0.4931849649794131</v>
+        <v>0.4931849649794862</v>
       </c>
       <c r="P7">
-        <v>0.7735594207261949</v>
+        <v>0.7609282793083719</v>
       </c>
       <c r="Q7">
-        <v>15.34097325963533</v>
+        <v>15.80538488283765</v>
       </c>
       <c r="R7">
-        <v>-96.35596489078564</v>
+        <v>-96.35596489078344</v>
       </c>
       <c r="S7">
-        <v>159.0146304036402</v>
+        <v>158.9172175563322</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13940,22 +13940,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.906379235289956</v>
+        <v>0.8967513406455306</v>
       </c>
       <c r="O8">
-        <v>0.6518511244056875</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P8">
-        <v>0.795785112763417</v>
+        <v>0.787165385765108</v>
       </c>
       <c r="Q8">
-        <v>16.96787656741729</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R8">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S8">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -14002,22 +14002,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.906379235289956</v>
+        <v>0.8967513406455307</v>
       </c>
       <c r="O9">
-        <v>0.6518511244056875</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P9">
-        <v>0.795785112763417</v>
+        <v>0.787165385765108</v>
       </c>
       <c r="Q9">
-        <v>16.96787656741729</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R9">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S9">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -15218,22 +15218,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.07630958169751</v>
+        <v>1.076309581697509</v>
       </c>
       <c r="O2">
-        <v>0.3968725684451604</v>
+        <v>0.3968725684451617</v>
       </c>
       <c r="P2">
-        <v>0.857503166648943</v>
+        <v>0.8575031666489434</v>
       </c>
       <c r="Q2">
-        <v>8.789108950209508</v>
+        <v>8.789108950209524</v>
       </c>
       <c r="R2">
-        <v>-124.0274590207982</v>
+        <v>-124.0274590207979</v>
       </c>
       <c r="S2">
-        <v>168.942911686649</v>
+        <v>168.9429116866488</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -15277,22 +15277,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.044105714997499</v>
+        <v>1.044105714997498</v>
       </c>
       <c r="O3">
-        <v>0.2604212734074323</v>
+        <v>0.2604212734074336</v>
       </c>
       <c r="P3">
         <v>0.8710642653707253</v>
       </c>
       <c r="Q3">
-        <v>5.325452027459386</v>
+        <v>5.325452027459407</v>
       </c>
       <c r="R3">
-        <v>-131.9071155621095</v>
+        <v>-131.907115562109</v>
       </c>
       <c r="S3">
-        <v>173.612583968783</v>
+        <v>173.6125839687828</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -15303,55 +15303,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.823703257666275</v>
+        <v>1.823703257666274</v>
       </c>
       <c r="D4">
-        <v>1.823703257666275</v>
+        <v>1.823703257666274</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>21.05831133471243</v>
+        <v>21.05831133471242</v>
       </c>
       <c r="G4">
-        <v>21.05831133471243</v>
+        <v>21.05831133471242</v>
       </c>
       <c r="H4">
-        <v>5.424025632034038</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I4">
-        <v>6.488939310918608</v>
+        <v>5.855913331295392</v>
       </c>
       <c r="J4">
-        <v>2.237816431607135</v>
+        <v>2.237816431607154</v>
       </c>
       <c r="K4">
-        <v>5.601194464564823</v>
+        <v>5.601194464564864</v>
       </c>
       <c r="L4">
-        <v>2.237816431580052</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M4">
-        <v>5.601194464517764</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N4">
-        <v>0.9526279648094363</v>
+        <v>0.9526279648094357</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648098424</v>
+        <v>0.9526279648098418</v>
       </c>
       <c r="Q4">
-        <v>-3.034760429830903E-13</v>
+        <v>-2.916474486782044E-13</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999999921</v>
+        <v>179.999999999992</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -15398,19 +15398,19 @@
         <v>1.044105714978375</v>
       </c>
       <c r="O5">
-        <v>0.2604212734211512</v>
+        <v>0.2604212734211528</v>
       </c>
       <c r="P5">
-        <v>0.8710642653956993</v>
+        <v>0.871064265395699</v>
       </c>
       <c r="Q5">
-        <v>5.325452029148319</v>
+        <v>5.325452029148345</v>
       </c>
       <c r="R5">
-        <v>-131.9071155464534</v>
+        <v>-131.907115546453</v>
       </c>
       <c r="S5">
-        <v>173.612583967056</v>
+        <v>173.6125839670559</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -15457,19 +15457,19 @@
         <v>1.044105714978375</v>
       </c>
       <c r="O6">
-        <v>0.2604212734211513</v>
+        <v>0.2604212734211525</v>
       </c>
       <c r="P6">
         <v>0.8710642653956993</v>
       </c>
       <c r="Q6">
-        <v>5.325452029148319</v>
+        <v>5.325452029148336</v>
       </c>
       <c r="R6">
-        <v>-131.9071155464534</v>
+        <v>-131.9071155464531</v>
       </c>
       <c r="S6">
-        <v>173.612583967056</v>
+        <v>173.6125839670559</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -15513,22 +15513,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9526279646260468</v>
+        <v>0.9526279646260464</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.9526279649932318</v>
+        <v>0.9526279649932312</v>
       </c>
       <c r="Q7">
-        <v>1.108245101224841E-09</v>
+        <v>1.108256929819179E-09</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9999999988835</v>
+        <v>179.9999999988834</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -15572,22 +15572,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.044105714823766</v>
+        <v>1.044105714823765</v>
       </c>
       <c r="O8">
-        <v>0.2604212731948777</v>
+        <v>0.2604212731948793</v>
       </c>
       <c r="P8">
         <v>0.8710642655471982</v>
       </c>
       <c r="Q8">
-        <v>5.325452029177776</v>
+        <v>5.325452029177803</v>
       </c>
       <c r="R8">
-        <v>-131.9071155000848</v>
+        <v>-131.9071155000843</v>
       </c>
       <c r="S8">
-        <v>173.612583969086</v>
+        <v>173.6125839690858</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -15631,22 +15631,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.044105714823766</v>
+        <v>1.044105714823765</v>
       </c>
       <c r="O9">
-        <v>0.2604212731948778</v>
+        <v>0.260421273194879</v>
       </c>
       <c r="P9">
         <v>0.8710642655471982</v>
       </c>
       <c r="Q9">
-        <v>5.325452029177776</v>
+        <v>5.325452029177792</v>
       </c>
       <c r="R9">
-        <v>-131.9071155000848</v>
+        <v>-131.9071155000844</v>
       </c>
       <c r="S9">
-        <v>173.612583969086</v>
+        <v>173.6125839690858</v>
       </c>
     </row>
   </sheetData>
